--- a/assets/LISTA ZAPATILLAS.xlsx
+++ b/assets/LISTA ZAPATILLAS.xlsx
@@ -5,16 +5,19 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manuel\Downloads\MilenaShoes\assets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d8bfe2c87cad12b0/IA/MILENASHOES/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98AC7BAF-207C-4AE8-B182-03C4C4295B86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{E0C42F5F-A3E4-4F22-AD40-E0497D996882}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15064101-52DF-41C6-93C1-27C93922BA61}"/>
   <bookViews>
-    <workbookView xWindow="10500" yWindow="390" windowWidth="18300" windowHeight="14580" xr2:uid="{B7A6A16F-7A19-4864-8939-1CF29A8D65F8}"/>
+    <workbookView xWindow="1545" yWindow="1125" windowWidth="15570" windowHeight="13710" xr2:uid="{B7A6A16F-7A19-4864-8939-1CF29A8D65F8}"/>
   </bookViews>
   <sheets>
     <sheet name="INVENTARIO" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">INVENTARIO!$B$2:$I$180</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -37,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="793" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="867" uniqueCount="128">
   <si>
     <t xml:space="preserve">NUMERO </t>
   </si>
@@ -78,15 +81,9 @@
     <t>ADIDAS</t>
   </si>
   <si>
-    <t>ADIDAS BOUNCE</t>
-  </si>
-  <si>
     <t>EU 36 AL 40</t>
   </si>
   <si>
-    <t>NIKE P7000</t>
-  </si>
-  <si>
     <t>EU 36 AL 39</t>
   </si>
   <si>
@@ -99,9 +96,6 @@
     <t>EU 36 AL 42</t>
   </si>
   <si>
-    <t>NIKE TRAIL</t>
-  </si>
-  <si>
     <t>SKECHERS</t>
   </si>
   <si>
@@ -126,45 +120,24 @@
     <t>ASICS RUN</t>
   </si>
   <si>
-    <t>NIKE P-7000</t>
-  </si>
-  <si>
     <t>NEW BALANCE</t>
   </si>
   <si>
     <t>ARMANI</t>
   </si>
   <si>
-    <t xml:space="preserve">ASICS RUN </t>
-  </si>
-  <si>
-    <t>ASCI RUN</t>
-  </si>
-  <si>
-    <t>NEWBALANCE RUN</t>
-  </si>
-  <si>
     <t xml:space="preserve">NEW BALANCE </t>
   </si>
   <si>
     <t>COACH</t>
   </si>
   <si>
-    <t xml:space="preserve">JORDAN </t>
-  </si>
-  <si>
-    <t>ORDAN RETRO 1 LOW</t>
-  </si>
-  <si>
     <t>SAMBA</t>
   </si>
   <si>
     <t xml:space="preserve">REEBOK </t>
   </si>
   <si>
-    <t>REBOOK CLUB</t>
-  </si>
-  <si>
     <t>LACOSTE</t>
   </si>
   <si>
@@ -174,30 +147,12 @@
     <t xml:space="preserve">VANS </t>
   </si>
   <si>
-    <t>VANS HYLANE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> VANS KNU</t>
-  </si>
-  <si>
-    <t>REBOOK FLOATZIG</t>
-  </si>
-  <si>
-    <t>NEW</t>
-  </si>
-  <si>
-    <t>BALANCE 740</t>
-  </si>
-  <si>
     <t>ZOOM PEGASUS</t>
   </si>
   <si>
     <t>SB PARRA</t>
   </si>
   <si>
-    <t>NIKE SB</t>
-  </si>
-  <si>
     <t xml:space="preserve">LACOSTE </t>
   </si>
   <si>
@@ -210,48 +165,21 @@
     <t xml:space="preserve">NIKE </t>
   </si>
   <si>
-    <t>NIKE AF1</t>
-  </si>
-  <si>
-    <t>RETRO 1</t>
-  </si>
-  <si>
     <t>LOUIS VUITTON</t>
   </si>
   <si>
     <t>SKATE</t>
   </si>
   <si>
-    <t>NIKE P-6000</t>
-  </si>
-  <si>
-    <t>NIKE P-6001</t>
-  </si>
-  <si>
     <t>ZOOM HAPPY</t>
   </si>
   <si>
-    <t>NKE</t>
-  </si>
-  <si>
-    <t>NIKE AIR MAX TN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NIKE SB DUNK </t>
-  </si>
-  <si>
     <t>JORDAN AURA</t>
   </si>
   <si>
     <t>SHOX GUSANO</t>
   </si>
   <si>
-    <t>LE COQ</t>
-  </si>
-  <si>
-    <t>SPORTIF</t>
-  </si>
-  <si>
     <t>EU 40 AL 46</t>
   </si>
   <si>
@@ -264,57 +192,30 @@
     <t>LACOSTE TABLA</t>
   </si>
   <si>
-    <t xml:space="preserve">NIKE AF1 </t>
-  </si>
-  <si>
     <t>PUMA</t>
   </si>
   <si>
-    <t>PUMA PARK</t>
-  </si>
-  <si>
-    <t>ADIDAD</t>
-  </si>
-  <si>
     <t>SUPERMAGMA</t>
   </si>
   <si>
     <t>INITIATOR</t>
   </si>
   <si>
-    <t>R1 LOW PARIS TOP</t>
-  </si>
-  <si>
     <t>JORDAN R3 TRAVIS SCOTT</t>
   </si>
   <si>
-    <t xml:space="preserve">JORDAN R3  </t>
-  </si>
-  <si>
     <t>JORDAN CLUB</t>
   </si>
   <si>
-    <t>ADIDAS SAMBA</t>
-  </si>
-  <si>
-    <t>PUMA SUEDE XL</t>
-  </si>
-  <si>
     <t>EU 36 AL 43</t>
   </si>
   <si>
     <t>GLOBE</t>
   </si>
   <si>
-    <t>GLOBE SKATE</t>
-  </si>
-  <si>
     <t xml:space="preserve">VANS  </t>
   </si>
   <si>
-    <t>VANS VISION</t>
-  </si>
-  <si>
     <t>JORDAN RETRO 1 LOW</t>
   </si>
   <si>
@@ -324,21 +225,6 @@
     <t xml:space="preserve">HYPERION MAX </t>
   </si>
   <si>
-    <t>NIKE AIR MAX 97</t>
-  </si>
-  <si>
-    <t>NIKE AIR MAX 2000</t>
-  </si>
-  <si>
-    <t>NIKE AIR MAX CORRELATE</t>
-  </si>
-  <si>
-    <t>NIKE NOCTA</t>
-  </si>
-  <si>
-    <t>NIKE TEKNO</t>
-  </si>
-  <si>
     <t xml:space="preserve">ADIDAS </t>
   </si>
   <si>
@@ -348,24 +234,9 @@
     <t>NIKE V2K</t>
   </si>
   <si>
-    <t>LECOQ SPORTIF</t>
-  </si>
-  <si>
-    <t>ADIDAS SL-72</t>
-  </si>
-  <si>
-    <t>NIKE SHOX</t>
-  </si>
-  <si>
     <t>CAMPUS</t>
   </si>
   <si>
-    <t>ADIDAS SUPERMAGMA</t>
-  </si>
-  <si>
-    <t>BALANCE 9060</t>
-  </si>
-  <si>
     <t>SB JARRITO</t>
   </si>
   <si>
@@ -375,9 +246,6 @@
     <t>JORDAN RETRO 11</t>
   </si>
   <si>
-    <t>REEBOK ANUEL</t>
-  </si>
-  <si>
     <t>ON CLOUD</t>
   </si>
   <si>
@@ -393,15 +261,6 @@
     <t>ALTRA</t>
   </si>
   <si>
-    <t>ALTRA TRAIL</t>
-  </si>
-  <si>
-    <t>RETRO</t>
-  </si>
-  <si>
-    <t>1 LOW PARIS PERLAS</t>
-  </si>
-  <si>
     <t>EQUIPMENT</t>
   </si>
   <si>
@@ -429,13 +288,142 @@
     <t>SHOX SUPREME</t>
   </si>
   <si>
-    <t>REBOOK ERA</t>
-  </si>
-  <si>
     <t>DISPONIBLE</t>
   </si>
   <si>
     <t>S</t>
+  </si>
+  <si>
+    <t>P-6000</t>
+  </si>
+  <si>
+    <t>X MOSTER</t>
+  </si>
+  <si>
+    <t>TERREX</t>
+  </si>
+  <si>
+    <t>TERREX GORETEX</t>
+  </si>
+  <si>
+    <t>RUNING</t>
+  </si>
+  <si>
+    <t>SPORT CABALLERO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUPER STAR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMAH </t>
+  </si>
+  <si>
+    <t xml:space="preserve">HYLANE </t>
+  </si>
+  <si>
+    <t>BOUNCE</t>
+  </si>
+  <si>
+    <t>SL-72</t>
+  </si>
+  <si>
+    <t>ASCIS RUN</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>LE COQ SPORTIF</t>
+  </si>
+  <si>
+    <t>RUN</t>
+  </si>
+  <si>
+    <t>SHOX</t>
+  </si>
+  <si>
+    <t>AF1</t>
+  </si>
+  <si>
+    <t>V2K</t>
+  </si>
+  <si>
+    <t>TEKNO</t>
+  </si>
+  <si>
+    <t>NOCTA</t>
+  </si>
+  <si>
+    <t>AIR MAX CORRELATE</t>
+  </si>
+  <si>
+    <t>AIR MAX 2000</t>
+  </si>
+  <si>
+    <t>AIR MAX 97</t>
+  </si>
+  <si>
+    <t>SB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AF1 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SB DUNK </t>
+  </si>
+  <si>
+    <t>AIR MAX TN</t>
+  </si>
+  <si>
+    <t>P-6001</t>
+  </si>
+  <si>
+    <t>P-7000</t>
+  </si>
+  <si>
+    <t>P7000</t>
+  </si>
+  <si>
+    <t>PARK</t>
+  </si>
+  <si>
+    <t>XL BMW</t>
+  </si>
+  <si>
+    <t>SUEDE XL</t>
+  </si>
+  <si>
+    <t>ANUEL</t>
+  </si>
+  <si>
+    <t>CLUB</t>
+  </si>
+  <si>
+    <t>FLOATZIG</t>
+  </si>
+  <si>
+    <t>ERA</t>
+  </si>
+  <si>
+    <t>HYLANE</t>
+  </si>
+  <si>
+    <t>KNU</t>
+  </si>
+  <si>
+    <t>VISION</t>
+  </si>
+  <si>
+    <t>JORDAN RETRO 1</t>
+  </si>
+  <si>
+    <t>JORDAN R1 LOW PARIS TOP</t>
+  </si>
+  <si>
+    <t>JORDAN R3</t>
+  </si>
+  <si>
+    <t>JORDAN LOW PARIS PERLAS</t>
   </si>
 </sst>
 </file>
@@ -465,7 +453,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -475,6 +463,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6C3FF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,26 +500,39 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -846,53 +853,53 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F75DB620-AF17-408B-81D4-431B9D551CF9}">
-  <dimension ref="B2:I163"/>
+  <dimension ref="B2:I189"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.42578125" customWidth="1"/>
-    <col min="2" max="2" width="14.140625" style="9" customWidth="1"/>
-    <col min="3" max="3" width="13.42578125" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16" style="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="5" t="s">
-        <v>131</v>
+      <c r="I2" s="4" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B3" s="6">
+      <c r="B3" s="5">
         <v>1</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="1" t="s">
+      <c r="C3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E3" s="1" t="s">
@@ -905,154 +912,160 @@
         <v>100000</v>
       </c>
       <c r="H3" s="2">
-        <v>160000</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>132</v>
+        <f>G3+45000</f>
+        <v>145000</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B4" s="6">
+      <c r="B4" s="5">
         <v>2</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="C4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="G4" s="2">
         <v>95000</v>
       </c>
       <c r="H4" s="2">
-        <v>155000</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>132</v>
+        <f t="shared" ref="H4:H67" si="0">G4+45000</f>
+        <v>140000</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B5" s="6">
+      <c r="B5" s="5">
         <v>3</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="1" t="s">
+      <c r="C5" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>15</v>
+        <v>113</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G5" s="2">
         <v>90000</v>
       </c>
       <c r="H5" s="2">
-        <v>150000</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="0"/>
+        <v>135000</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B6" s="6">
+      <c r="B6" s="5">
         <v>4</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="1" t="s">
+      <c r="C6" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G6" s="2">
         <v>70000</v>
       </c>
       <c r="H6" s="2">
-        <v>130000</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="0"/>
+        <v>115000</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B7" s="6">
+      <c r="B7" s="5">
         <v>5</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="1" t="s">
+      <c r="C7" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G7" s="2">
         <v>70000</v>
       </c>
       <c r="H7" s="2">
-        <v>130000</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="0"/>
+        <v>115000</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B8" s="6">
+      <c r="B8" s="5">
         <v>6</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="1" t="s">
+      <c r="C8" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="G8" s="2">
         <v>70000</v>
       </c>
       <c r="H8" s="2">
-        <v>130000</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="0"/>
+        <v>115000</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B9" s="6">
-        <v>7</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" s="1" t="s">
+      <c r="B9" s="5">
+        <v>7</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>20</v>
+        <v>74</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>11</v>
@@ -1061,24 +1074,25 @@
         <v>90000</v>
       </c>
       <c r="H9" s="2">
-        <v>150000</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="0"/>
+        <v>135000</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B10" s="6">
-        <v>8</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>21</v>
+      <c r="B10" s="5">
+        <v>8</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>18</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>11</v>
@@ -1087,102 +1101,106 @@
         <v>90000</v>
       </c>
       <c r="H10" s="2">
-        <v>150000</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="0"/>
+        <v>135000</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B11" s="6">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>21</v>
+      <c r="B11" s="5">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>18</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G11" s="2">
         <v>90000</v>
       </c>
       <c r="H11" s="2">
-        <v>150000</v>
-      </c>
-      <c r="I11" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="0"/>
+        <v>135000</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B12" s="6">
+      <c r="B12" s="5">
         <v>10</v>
       </c>
-      <c r="C12" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D12" s="1" t="s">
+      <c r="C12" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G12" s="2">
         <v>85000</v>
       </c>
       <c r="H12" s="2">
-        <v>145000</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="0"/>
+        <v>130000</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B13" s="6">
-        <v>11</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13" s="1" t="s">
+      <c r="B13" s="5">
+        <v>11</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G13" s="2">
         <v>85000</v>
       </c>
       <c r="H13" s="2">
-        <v>145000</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="0"/>
+        <v>130000</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B14" s="6">
+      <c r="B14" s="5">
         <v>12</v>
       </c>
-      <c r="C14" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>27</v>
+      <c r="C14" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>24</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>11</v>
@@ -1191,24 +1209,25 @@
         <v>90000</v>
       </c>
       <c r="H14" s="2">
-        <v>150000</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="0"/>
+        <v>135000</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B15" s="6">
+      <c r="B15" s="5">
         <v>13</v>
       </c>
-      <c r="C15" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D15" s="1" t="s">
+      <c r="C15" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>29</v>
+        <v>112</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>11</v>
@@ -1217,24 +1236,25 @@
         <v>85000</v>
       </c>
       <c r="H15" s="2">
-        <v>145000</v>
-      </c>
-      <c r="I15" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="0"/>
+        <v>130000</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B16" s="6">
+      <c r="B16" s="5">
         <v>14</v>
       </c>
-      <c r="C16" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D16" s="1" t="s">
+      <c r="C16" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>29</v>
+        <v>112</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>11</v>
@@ -1243,50 +1263,52 @@
         <v>85000</v>
       </c>
       <c r="H16" s="2">
-        <v>145000</v>
-      </c>
-      <c r="I16" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="0"/>
+        <v>130000</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B17" s="6">
+      <c r="B17" s="5">
         <v>15</v>
       </c>
-      <c r="C17" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>30</v>
+      <c r="C17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>26</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G17" s="2">
         <v>85000</v>
       </c>
       <c r="H17" s="2">
-        <v>145000</v>
-      </c>
-      <c r="I17" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="0"/>
+        <v>130000</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B18" s="6">
+      <c r="B18" s="5">
         <v>16</v>
       </c>
-      <c r="C18" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>31</v>
+      <c r="C18" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>27</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>11</v>
@@ -1295,24 +1317,25 @@
         <v>80000</v>
       </c>
       <c r="H18" s="2">
-        <v>140000</v>
-      </c>
-      <c r="I18" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="0"/>
+        <v>125000</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B19" s="6">
+      <c r="B19" s="5">
         <v>17</v>
       </c>
-      <c r="C19" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>31</v>
+      <c r="C19" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>27</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>11</v>
@@ -1321,24 +1344,25 @@
         <v>80000</v>
       </c>
       <c r="H19" s="2">
-        <v>140000</v>
-      </c>
-      <c r="I19" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="0"/>
+        <v>125000</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B20" s="6">
+      <c r="B20" s="5">
         <v>18</v>
       </c>
-      <c r="C20" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>21</v>
+      <c r="C20" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>18</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>11</v>
@@ -1347,24 +1371,25 @@
         <v>90000</v>
       </c>
       <c r="H20" s="2">
-        <v>150000</v>
-      </c>
-      <c r="I20" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="0"/>
+        <v>135000</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B21" s="6">
+      <c r="B21" s="5">
         <v>19</v>
       </c>
-      <c r="C21" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>32</v>
+      <c r="C21" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21" s="13" t="s">
+        <v>24</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>33</v>
+        <v>95</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>11</v>
@@ -1373,24 +1398,25 @@
         <v>80000</v>
       </c>
       <c r="H21" s="2">
-        <v>140000</v>
-      </c>
-      <c r="I21" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="0"/>
+        <v>125000</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B22" s="6">
+      <c r="B22" s="5">
         <v>20</v>
       </c>
-      <c r="C22" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>30</v>
+      <c r="C22" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>26</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>11</v>
@@ -1399,24 +1425,25 @@
         <v>80000</v>
       </c>
       <c r="H22" s="2">
-        <v>140000</v>
-      </c>
-      <c r="I22" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="0"/>
+        <v>125000</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B23" s="6">
+      <c r="B23" s="5">
         <v>21</v>
       </c>
-      <c r="C23" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>35</v>
+      <c r="C23" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>28</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>11</v>
@@ -1425,24 +1452,25 @@
         <v>85000</v>
       </c>
       <c r="H23" s="2">
-        <v>145000</v>
-      </c>
-      <c r="I23" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="0"/>
+        <v>130000</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B24" s="6">
+      <c r="B24" s="5">
         <v>22</v>
       </c>
-      <c r="C24" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>36</v>
+      <c r="C24" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>29</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>11</v>
@@ -1451,24 +1479,25 @@
         <v>80000</v>
       </c>
       <c r="H24" s="2">
-        <v>140000</v>
-      </c>
-      <c r="I24" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="0"/>
+        <v>125000</v>
+      </c>
+      <c r="I24" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B25" s="6">
+      <c r="B25" s="5">
         <v>23</v>
       </c>
-      <c r="C25" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>37</v>
+      <c r="C25" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>9</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>11</v>
@@ -1477,50 +1506,52 @@
         <v>95000</v>
       </c>
       <c r="H25" s="2">
-        <v>155000</v>
-      </c>
-      <c r="I25" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="0"/>
+        <v>140000</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B26" s="6">
+      <c r="B26" s="5">
         <v>24</v>
       </c>
-      <c r="C26" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>39</v>
+      <c r="C26" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>30</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G26" s="2">
         <v>100000</v>
       </c>
       <c r="H26" s="2">
-        <v>160000</v>
-      </c>
-      <c r="I26" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="0"/>
+        <v>145000</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B27" s="6">
+      <c r="B27" s="5">
         <v>25</v>
       </c>
-      <c r="C27" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>40</v>
+      <c r="C27" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>31</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>41</v>
+        <v>118</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>11</v>
@@ -1529,24 +1560,25 @@
         <v>95000</v>
       </c>
       <c r="H27" s="2">
-        <v>155000</v>
-      </c>
-      <c r="I27" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="0"/>
+        <v>140000</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B28" s="6">
+      <c r="B28" s="5">
         <v>26</v>
       </c>
-      <c r="C28" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>42</v>
+      <c r="C28" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>32</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>11</v>
@@ -1555,76 +1587,79 @@
         <v>95000</v>
       </c>
       <c r="H28" s="2">
-        <v>155000</v>
-      </c>
-      <c r="I28" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="0"/>
+        <v>140000</v>
+      </c>
+      <c r="I28" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B29" s="6">
+      <c r="B29" s="5">
         <v>27</v>
       </c>
-      <c r="C29" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>44</v>
+      <c r="C29" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>34</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>45</v>
+        <v>121</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G29" s="2">
         <v>110000</v>
       </c>
       <c r="H29" s="2">
-        <v>170000</v>
-      </c>
-      <c r="I29" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="0"/>
+        <v>155000</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B30" s="6">
+      <c r="B30" s="5">
         <v>28</v>
       </c>
-      <c r="C30" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>44</v>
+      <c r="C30" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>34</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>46</v>
+        <v>122</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G30" s="2">
         <v>100000</v>
       </c>
       <c r="H30" s="2">
-        <v>160000</v>
-      </c>
-      <c r="I30" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="0"/>
+        <v>145000</v>
+      </c>
+      <c r="I30" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B31" s="6">
+      <c r="B31" s="5">
         <v>29</v>
       </c>
-      <c r="C31" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>40</v>
+      <c r="C31" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D31" s="13" t="s">
+        <v>31</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>47</v>
+        <v>119</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>11</v>
@@ -1633,50 +1668,52 @@
         <v>80000</v>
       </c>
       <c r="H31" s="2">
-        <v>140000</v>
-      </c>
-      <c r="I31" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="0"/>
+        <v>125000</v>
+      </c>
+      <c r="I31" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B32" s="6">
+      <c r="B32" s="5">
         <v>30</v>
       </c>
-      <c r="C32" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>49</v>
+      <c r="C32" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D32" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="E32" s="1">
+        <v>740</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G32" s="2">
         <v>75000</v>
       </c>
       <c r="H32" s="2">
-        <v>135000</v>
-      </c>
-      <c r="I32" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="0"/>
+        <v>120000</v>
+      </c>
+      <c r="I32" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="33" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B33" s="6">
+      <c r="B33" s="5">
         <v>31</v>
       </c>
-      <c r="C33" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D33" s="1" t="s">
+      <c r="C33" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D33" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>11</v>
@@ -1685,50 +1722,52 @@
         <v>80000</v>
       </c>
       <c r="H33" s="2">
-        <v>140000</v>
-      </c>
-      <c r="I33" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="0"/>
+        <v>125000</v>
+      </c>
+      <c r="I33" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B34" s="6">
+      <c r="B34" s="5">
         <v>32</v>
       </c>
-      <c r="C34" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D34" s="1" t="s">
+      <c r="C34" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G34" s="2">
         <v>95000</v>
       </c>
       <c r="H34" s="2">
-        <v>155000</v>
-      </c>
-      <c r="I34" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="0"/>
+        <v>140000</v>
+      </c>
+      <c r="I34" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="35" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B35" s="6">
+      <c r="B35" s="5">
         <v>33</v>
       </c>
-      <c r="C35" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D35" s="1" t="s">
+      <c r="C35" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D35" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>52</v>
+        <v>107</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>11</v>
@@ -1737,24 +1776,25 @@
         <v>95000</v>
       </c>
       <c r="H35" s="2">
-        <v>155000</v>
-      </c>
-      <c r="I35" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="0"/>
+        <v>140000</v>
+      </c>
+      <c r="I35" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="36" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B36" s="6">
+      <c r="B36" s="5">
         <v>34</v>
       </c>
-      <c r="C36" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>42</v>
+      <c r="C36" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D36" s="13" t="s">
+        <v>32</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>11</v>
@@ -1763,76 +1803,79 @@
         <v>90000</v>
       </c>
       <c r="H36" s="2">
-        <v>150000</v>
-      </c>
-      <c r="I36" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="0"/>
+        <v>135000</v>
+      </c>
+      <c r="I36" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="37" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B37" s="6">
+      <c r="B37" s="5">
         <v>35</v>
       </c>
-      <c r="C37" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D37" s="1" t="s">
+      <c r="C37" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D37" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G37" s="2">
         <v>95000</v>
       </c>
       <c r="H37" s="2">
-        <v>155000</v>
-      </c>
-      <c r="I37" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="0"/>
+        <v>140000</v>
+      </c>
+      <c r="I37" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="38" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B38" s="6">
+      <c r="B38" s="5">
         <v>36</v>
       </c>
-      <c r="C38" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D38" s="1" t="s">
+      <c r="C38" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>52</v>
+        <v>107</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G38" s="2">
         <v>95000</v>
       </c>
       <c r="H38" s="2">
-        <v>155000</v>
-      </c>
-      <c r="I38" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="0"/>
+        <v>140000</v>
+      </c>
+      <c r="I38" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="39" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B39" s="6">
+      <c r="B39" s="5">
         <v>37</v>
       </c>
-      <c r="C39" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D39" s="1" t="s">
+      <c r="C39" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D39" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>11</v>
@@ -1841,24 +1884,25 @@
         <v>95000</v>
       </c>
       <c r="H39" s="2">
-        <v>155000</v>
-      </c>
-      <c r="I39" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="0"/>
+        <v>140000</v>
+      </c>
+      <c r="I39" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="40" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B40" s="6">
+      <c r="B40" s="5">
         <v>38</v>
       </c>
-      <c r="C40" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>56</v>
+      <c r="C40" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D40" s="13" t="s">
+        <v>40</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>57</v>
+        <v>100</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>11</v>
@@ -1867,154 +1911,160 @@
         <v>95000</v>
       </c>
       <c r="H40" s="2">
-        <v>155000</v>
-      </c>
-      <c r="I40" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="0"/>
+        <v>140000</v>
+      </c>
+      <c r="I40" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B41" s="6">
+      <c r="B41" s="5">
         <v>39</v>
       </c>
-      <c r="C41" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>37</v>
+      <c r="C41" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D41" s="13" t="s">
+        <v>9</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>58</v>
+        <v>124</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G41" s="2">
         <v>90000</v>
       </c>
       <c r="H41" s="2">
-        <v>150000</v>
-      </c>
-      <c r="I41" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="0"/>
+        <v>135000</v>
+      </c>
+      <c r="I41" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="42" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B42" s="6">
+      <c r="B42" s="5">
         <v>40</v>
       </c>
-      <c r="C42" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>59</v>
+      <c r="C42" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D42" s="13" t="s">
+        <v>41</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G42" s="2">
         <v>90000</v>
       </c>
       <c r="H42" s="2">
-        <v>150000</v>
-      </c>
-      <c r="I42" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="0"/>
+        <v>135000</v>
+      </c>
+      <c r="I42" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="43" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B43" s="6">
+      <c r="B43" s="5">
         <v>41</v>
       </c>
-      <c r="C43" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D43" s="1" t="s">
+      <c r="C43" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D43" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G43" s="2">
         <v>100000</v>
       </c>
       <c r="H43" s="2">
-        <v>160000</v>
-      </c>
-      <c r="I43" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="0"/>
+        <v>145000</v>
+      </c>
+      <c r="I43" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="44" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B44" s="6">
+      <c r="B44" s="5">
         <v>42</v>
       </c>
-      <c r="C44" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D44" s="1" t="s">
+      <c r="C44" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D44" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>62</v>
+        <v>111</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G44" s="2">
         <v>100000</v>
       </c>
       <c r="H44" s="2">
-        <v>160000</v>
-      </c>
-      <c r="I44" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="0"/>
+        <v>145000</v>
+      </c>
+      <c r="I44" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="45" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B45" s="6">
+      <c r="B45" s="5">
         <v>43</v>
       </c>
-      <c r="C45" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D45" s="1" t="s">
+      <c r="C45" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D45" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G45" s="2">
         <v>90000</v>
       </c>
       <c r="H45" s="2">
-        <v>150000</v>
-      </c>
-      <c r="I45" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="0"/>
+        <v>135000</v>
+      </c>
+      <c r="I45" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="46" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B46" s="6">
+      <c r="B46" s="5">
         <v>44</v>
       </c>
-      <c r="C46" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>64</v>
+      <c r="C46" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D46" s="13" t="s">
+        <v>9</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>65</v>
+        <v>110</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>11</v>
@@ -2023,24 +2073,25 @@
         <v>85000</v>
       </c>
       <c r="H46" s="2">
-        <v>145000</v>
-      </c>
-      <c r="I46" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="0"/>
+        <v>130000</v>
+      </c>
+      <c r="I46" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="47" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B47" s="6">
+      <c r="B47" s="5">
         <v>45</v>
       </c>
-      <c r="C47" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D47" s="1" t="s">
+      <c r="C47" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D47" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>66</v>
+        <v>109</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>11</v>
@@ -2049,24 +2100,25 @@
         <v>95000</v>
       </c>
       <c r="H47" s="2">
-        <v>155000</v>
-      </c>
-      <c r="I47" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="0"/>
+        <v>140000</v>
+      </c>
+      <c r="I47" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="48" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B48" s="6">
+      <c r="B48" s="5">
         <v>46</v>
       </c>
-      <c r="C48" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D48" s="1" t="s">
+      <c r="C48" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D48" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>66</v>
+        <v>109</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>11</v>
@@ -2075,50 +2127,52 @@
         <v>95000</v>
       </c>
       <c r="H48" s="2">
-        <v>155000</v>
-      </c>
-      <c r="I48" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="0"/>
+        <v>140000</v>
+      </c>
+      <c r="I48" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="49" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B49" s="6">
+      <c r="B49" s="5">
         <v>47</v>
       </c>
-      <c r="C49" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D49" s="1" t="s">
+      <c r="C49" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D49" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>66</v>
+        <v>109</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G49" s="2">
         <v>100000</v>
       </c>
       <c r="H49" s="2">
-        <v>160000</v>
-      </c>
-      <c r="I49" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="0"/>
+        <v>145000</v>
+      </c>
+      <c r="I49" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="50" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B50" s="6">
+      <c r="B50" s="5">
         <v>48</v>
       </c>
-      <c r="C50" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>37</v>
+      <c r="C50" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D50" s="13" t="s">
+        <v>9</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>11</v>
@@ -2127,24 +2181,25 @@
         <v>110000</v>
       </c>
       <c r="H50" s="2">
-        <v>170000</v>
-      </c>
-      <c r="I50" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="0"/>
+        <v>155000</v>
+      </c>
+      <c r="I50" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="51" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B51" s="6">
+      <c r="B51" s="5">
         <v>49</v>
       </c>
-      <c r="C51" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>37</v>
+      <c r="C51" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D51" s="13" t="s">
+        <v>9</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>11</v>
@@ -2153,50 +2208,52 @@
         <v>110000</v>
       </c>
       <c r="H51" s="2">
-        <v>170000</v>
-      </c>
-      <c r="I51" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="0"/>
+        <v>155000</v>
+      </c>
+      <c r="I51" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B52" s="6">
+      <c r="B52" s="5">
         <v>50</v>
       </c>
-      <c r="C52" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D52" s="1" t="s">
+      <c r="C52" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D52" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G52" s="2">
         <v>100000</v>
       </c>
       <c r="H52" s="2">
-        <v>160000</v>
-      </c>
-      <c r="I52" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="0"/>
+        <v>145000</v>
+      </c>
+      <c r="I52" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B53" s="6">
+      <c r="B53" s="5">
         <v>51</v>
       </c>
-      <c r="C53" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>69</v>
+      <c r="C53" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D53" s="13" t="s">
+        <v>97</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>11</v>
@@ -2205,128 +2262,133 @@
         <v>90000</v>
       </c>
       <c r="H53" s="2">
-        <v>150000</v>
-      </c>
-      <c r="I53" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="0"/>
+        <v>135000</v>
+      </c>
+      <c r="I53" s="5" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B54" s="6">
+      <c r="B54" s="5">
         <v>52</v>
       </c>
-      <c r="C54" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>69</v>
+      <c r="C54" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D54" s="13" t="s">
+        <v>97</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G54" s="2">
         <v>95000</v>
       </c>
       <c r="H54" s="2">
-        <v>155000</v>
-      </c>
-      <c r="I54" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="0"/>
+        <v>140000</v>
+      </c>
+      <c r="I54" s="5" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B55" s="6">
+      <c r="B55" s="5">
         <v>53</v>
       </c>
-      <c r="C55" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>69</v>
+      <c r="C55" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D55" s="13" t="s">
+        <v>97</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="G55" s="2">
         <v>95000</v>
       </c>
       <c r="H55" s="2">
-        <v>155000</v>
-      </c>
-      <c r="I55" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="0"/>
+        <v>140000</v>
+      </c>
+      <c r="I55" s="5" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="56" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B56" s="6">
+      <c r="B56" s="5">
         <v>54</v>
       </c>
-      <c r="C56" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>69</v>
+      <c r="C56" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D56" s="13" t="s">
+        <v>97</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="G56" s="2">
         <v>95000</v>
       </c>
       <c r="H56" s="2">
-        <v>155000</v>
-      </c>
-      <c r="I56" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="0"/>
+        <v>140000</v>
+      </c>
+      <c r="I56" s="5" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="57" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B57" s="6">
+      <c r="B57" s="5">
         <v>55</v>
       </c>
-      <c r="C57" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>69</v>
+      <c r="C57" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D57" s="13" t="s">
+        <v>97</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="G57" s="2">
         <v>95000</v>
       </c>
       <c r="H57" s="2">
-        <v>155000</v>
-      </c>
-      <c r="I57" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="0"/>
+        <v>140000</v>
+      </c>
+      <c r="I57" s="5" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="58" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B58" s="6">
+      <c r="B58" s="5">
         <v>56</v>
       </c>
-      <c r="C58" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>42</v>
+      <c r="C58" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D58" s="13" t="s">
+        <v>32</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>11</v>
@@ -2335,24 +2397,25 @@
         <v>100000</v>
       </c>
       <c r="H58" s="2">
-        <v>160000</v>
-      </c>
-      <c r="I58" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="0"/>
+        <v>145000</v>
+      </c>
+      <c r="I58" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="59" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B59" s="6">
+      <c r="B59" s="5">
         <v>57</v>
       </c>
-      <c r="C59" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>56</v>
+      <c r="C59" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D59" s="13" t="s">
+        <v>40</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>75</v>
+        <v>108</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>11</v>
@@ -2361,124 +2424,129 @@
         <v>75000</v>
       </c>
       <c r="H59" s="2">
-        <v>135000</v>
-      </c>
-      <c r="I59" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="0"/>
+        <v>120000</v>
+      </c>
+      <c r="I59" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="60" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B60" s="6">
+      <c r="B60" s="5">
         <v>58</v>
       </c>
-      <c r="C60" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D60" s="1" t="s">
+      <c r="C60" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D60" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>20</v>
+        <v>74</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G60" s="2">
         <v>85000</v>
       </c>
       <c r="H60" s="2">
-        <v>145000</v>
-      </c>
-      <c r="I60" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="0"/>
+        <v>130000</v>
+      </c>
+      <c r="I60" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="61" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B61" s="6">
+      <c r="B61" s="5">
         <v>59</v>
       </c>
-      <c r="C61" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>76</v>
+      <c r="C61" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D61" s="13" t="s">
+        <v>50</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G61" s="2">
         <v>95000</v>
       </c>
       <c r="H61" s="2">
-        <v>155000</v>
-      </c>
-      <c r="I61" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="0"/>
+        <v>140000</v>
+      </c>
+      <c r="I61" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="62" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B62" s="6">
+      <c r="B62" s="5">
         <v>60</v>
       </c>
-      <c r="C62" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>76</v>
+      <c r="C62" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D62" s="13" t="s">
+        <v>50</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G62" s="2">
         <v>95000</v>
       </c>
       <c r="H62" s="2">
-        <v>155000</v>
-      </c>
-      <c r="I62" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="0"/>
+        <v>140000</v>
+      </c>
+      <c r="I62" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="63" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B63" s="6">
+      <c r="B63" s="5">
         <v>61</v>
       </c>
-      <c r="C63" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>76</v>
+      <c r="C63" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D63" s="13" t="s">
+        <v>50</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G63" s="2">
         <v>95000</v>
       </c>
       <c r="H63" s="2">
-        <v>155000</v>
-      </c>
-      <c r="I63" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="0"/>
+        <v>140000</v>
+      </c>
+      <c r="I63" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="64" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B64" s="6">
+      <c r="B64" s="5">
         <v>62</v>
       </c>
-      <c r="C64" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D64" s="1" t="s">
+      <c r="C64" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D64" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E64" s="1" t="s">
@@ -2491,20 +2559,21 @@
         <v>95000</v>
       </c>
       <c r="H64" s="2">
-        <v>155000</v>
-      </c>
-      <c r="I64" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="0"/>
+        <v>140000</v>
+      </c>
+      <c r="I64" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="65" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B65" s="6">
+      <c r="B65" s="5">
         <v>63</v>
       </c>
-      <c r="C65" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D65" s="1" t="s">
+      <c r="C65" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D65" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E65" s="1" t="s">
@@ -2517,20 +2586,21 @@
         <v>95000</v>
       </c>
       <c r="H65" s="2">
-        <v>155000</v>
-      </c>
-      <c r="I65" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="0"/>
+        <v>140000</v>
+      </c>
+      <c r="I65" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="66" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B66" s="6">
+      <c r="B66" s="5">
         <v>64</v>
       </c>
-      <c r="C66" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D66" s="1" t="s">
+      <c r="C66" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D66" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E66" s="1" t="s">
@@ -2543,20 +2613,21 @@
         <v>95000</v>
       </c>
       <c r="H66" s="2">
-        <v>155000</v>
-      </c>
-      <c r="I66" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="0"/>
+        <v>140000</v>
+      </c>
+      <c r="I66" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="67" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B67" s="6">
+      <c r="B67" s="5">
         <v>65</v>
       </c>
-      <c r="C67" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D67" s="1" t="s">
+      <c r="C67" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D67" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E67" s="1" t="s">
@@ -2569,466 +2640,484 @@
         <v>95000</v>
       </c>
       <c r="H67" s="2">
-        <v>155000</v>
-      </c>
-      <c r="I67" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="0"/>
+        <v>140000</v>
+      </c>
+      <c r="I67" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="68" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B68" s="6">
+      <c r="B68" s="5">
         <v>66</v>
       </c>
-      <c r="C68" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>78</v>
+      <c r="C68" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D68" s="13" t="s">
+        <v>12</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G68" s="2">
         <v>110000</v>
       </c>
       <c r="H68" s="2">
-        <v>170000</v>
-      </c>
-      <c r="I68" s="6" t="s">
-        <v>132</v>
+        <f t="shared" ref="H68:H131" si="1">G68+45000</f>
+        <v>155000</v>
+      </c>
+      <c r="I68" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="69" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B69" s="6">
+      <c r="B69" s="5">
         <v>67</v>
       </c>
-      <c r="C69" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D69" s="1" t="s">
+      <c r="C69" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D69" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>80</v>
+        <v>52</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G69" s="2">
         <v>100000</v>
       </c>
       <c r="H69" s="2">
-        <v>160000</v>
-      </c>
-      <c r="I69" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="1"/>
+        <v>145000</v>
+      </c>
+      <c r="I69" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="70" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B70" s="6">
+      <c r="B70" s="5">
         <v>68</v>
       </c>
-      <c r="C70" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>37</v>
+      <c r="C70" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D70" s="13" t="s">
+        <v>9</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>81</v>
+        <v>125</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G70" s="2">
         <v>100000</v>
       </c>
       <c r="H70" s="2">
-        <v>160000</v>
-      </c>
-      <c r="I70" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="1"/>
+        <v>145000</v>
+      </c>
+      <c r="I70" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="71" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B71" s="6">
+      <c r="B71" s="5">
         <v>69</v>
       </c>
-      <c r="C71" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>37</v>
+      <c r="C71" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D71" s="13" t="s">
+        <v>9</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G71" s="2">
         <v>100000</v>
       </c>
       <c r="H71" s="2">
-        <v>160000</v>
-      </c>
-      <c r="I71" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="1"/>
+        <v>145000</v>
+      </c>
+      <c r="I71" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="72" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B72" s="6">
+      <c r="B72" s="5">
         <v>70</v>
       </c>
-      <c r="C72" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>37</v>
+      <c r="C72" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D72" s="13" t="s">
+        <v>9</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>83</v>
+        <v>126</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G72" s="2">
         <v>110000</v>
       </c>
       <c r="H72" s="2">
-        <v>170000</v>
-      </c>
-      <c r="I72" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="1"/>
+        <v>155000</v>
+      </c>
+      <c r="I72" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="73" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B73" s="6">
+      <c r="B73" s="5">
         <v>71</v>
       </c>
-      <c r="C73" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>40</v>
+      <c r="C73" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D73" s="13" t="s">
+        <v>31</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>84</v>
+        <v>54</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G73" s="2">
         <v>95000</v>
       </c>
       <c r="H73" s="2">
-        <v>155000</v>
-      </c>
-      <c r="I73" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="1"/>
+        <v>140000</v>
+      </c>
+      <c r="I73" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="74" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B74" s="6">
+      <c r="B74" s="5">
         <v>72</v>
       </c>
-      <c r="C74" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D74" s="1" t="s">
+      <c r="C74" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D74" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>85</v>
+        <v>30</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G74" s="2">
         <v>75000</v>
       </c>
       <c r="H74" s="2">
-        <v>135000</v>
-      </c>
-      <c r="I74" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="1"/>
+        <v>120000</v>
+      </c>
+      <c r="I74" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="75" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B75" s="6">
+      <c r="B75" s="5">
         <v>73</v>
       </c>
-      <c r="C75" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>76</v>
+      <c r="C75" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D75" s="13" t="s">
+        <v>50</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>86</v>
+        <v>116</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G75" s="2">
         <v>95000</v>
       </c>
       <c r="H75" s="2">
-        <v>155000</v>
-      </c>
-      <c r="I75" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="1"/>
+        <v>140000</v>
+      </c>
+      <c r="I75" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="76" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B76" s="6">
+      <c r="B76" s="5">
         <v>74</v>
       </c>
-      <c r="C76" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>76</v>
+      <c r="C76" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D76" s="13" t="s">
+        <v>50</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G76" s="2">
         <v>100000</v>
       </c>
       <c r="H76" s="2">
-        <v>160000</v>
-      </c>
-      <c r="I76" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="1"/>
+        <v>145000</v>
+      </c>
+      <c r="I76" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="77" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B77" s="6">
+      <c r="B77" s="5">
         <v>75</v>
       </c>
-      <c r="C77" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D77" s="1" t="s">
+      <c r="C77" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D77" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>52</v>
+        <v>107</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G77" s="2">
         <v>110000</v>
       </c>
       <c r="H77" s="2">
-        <v>170000</v>
-      </c>
-      <c r="I77" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="1"/>
+        <v>155000</v>
+      </c>
+      <c r="I77" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="78" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B78" s="6">
+      <c r="B78" s="5">
         <v>76</v>
       </c>
-      <c r="C78" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D78" s="1" t="s">
+      <c r="C78" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D78" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>52</v>
+        <v>107</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G78" s="2">
         <v>110000</v>
       </c>
       <c r="H78" s="2">
-        <v>170000</v>
-      </c>
-      <c r="I78" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="1"/>
+        <v>155000</v>
+      </c>
+      <c r="I78" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="79" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B79" s="6">
+      <c r="B79" s="5">
         <v>77</v>
       </c>
-      <c r="C79" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D79" s="1" t="s">
+      <c r="C79" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D79" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>52</v>
+        <v>107</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G79" s="2">
         <v>110000</v>
       </c>
       <c r="H79" s="2">
-        <v>170000</v>
-      </c>
-      <c r="I79" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="1"/>
+        <v>155000</v>
+      </c>
+      <c r="I79" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="80" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B80" s="6">
+      <c r="B80" s="5">
         <v>78</v>
       </c>
-      <c r="C80" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D80" s="1" t="s">
+      <c r="C80" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D80" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>52</v>
+        <v>107</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>87</v>
+        <v>55</v>
       </c>
       <c r="G80" s="2">
         <v>90000</v>
       </c>
       <c r="H80" s="2">
-        <v>150000</v>
-      </c>
-      <c r="I80" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="1"/>
+        <v>135000</v>
+      </c>
+      <c r="I80" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="81" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B81" s="6">
+      <c r="B81" s="5">
         <v>79</v>
       </c>
-      <c r="C81" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D81" s="1" t="s">
+      <c r="C81" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D81" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>52</v>
+        <v>107</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G81" s="2">
         <v>90000</v>
       </c>
       <c r="H81" s="2">
-        <v>150000</v>
-      </c>
-      <c r="I81" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="1"/>
+        <v>135000</v>
+      </c>
+      <c r="I81" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="82" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B82" s="6">
+      <c r="B82" s="5">
         <v>80</v>
       </c>
-      <c r="C82" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D82" s="1" t="s">
+      <c r="C82" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D82" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>52</v>
+        <v>107</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G82" s="2">
         <v>90000</v>
       </c>
       <c r="H82" s="2">
-        <v>150000</v>
-      </c>
-      <c r="I82" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="1"/>
+        <v>135000</v>
+      </c>
+      <c r="I82" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="83" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B83" s="6">
+      <c r="B83" s="5">
         <v>81</v>
       </c>
-      <c r="C83" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D83" s="1" t="s">
+      <c r="C83" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D83" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>52</v>
+        <v>107</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G83" s="2">
         <v>90000</v>
       </c>
       <c r="H83" s="2">
-        <v>150000</v>
-      </c>
-      <c r="I83" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="1"/>
+        <v>135000</v>
+      </c>
+      <c r="I83" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="84" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B84" s="6">
+      <c r="B84" s="5">
         <v>82</v>
       </c>
-      <c r="C84" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D84" s="1" t="s">
+      <c r="C84" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D84" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>52</v>
+        <v>107</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G84" s="2">
         <v>90000</v>
       </c>
       <c r="H84" s="2">
-        <v>150000</v>
-      </c>
-      <c r="I84" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="1"/>
+        <v>135000</v>
+      </c>
+      <c r="I84" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B85" s="6">
-        <v>83</v>
-      </c>
-      <c r="C85" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D85" s="1" t="s">
+      <c r="B85" s="5">
+        <v>83</v>
+      </c>
+      <c r="C85" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D85" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>52</v>
+        <v>107</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>11</v>
@@ -3037,24 +3126,25 @@
         <v>90000</v>
       </c>
       <c r="H85" s="2">
-        <v>150000</v>
-      </c>
-      <c r="I85" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="1"/>
+        <v>135000</v>
+      </c>
+      <c r="I85" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="86" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B86" s="6">
+      <c r="B86" s="5">
         <v>84</v>
       </c>
-      <c r="C86" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>88</v>
+      <c r="C86" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D86" s="13" t="s">
+        <v>56</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>89</v>
+        <v>42</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>11</v>
@@ -3063,24 +3153,25 @@
         <v>105000</v>
       </c>
       <c r="H86" s="2">
-        <v>165000</v>
-      </c>
-      <c r="I86" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="1"/>
+        <v>150000</v>
+      </c>
+      <c r="I86" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="87" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B87" s="6">
+      <c r="B87" s="5">
         <v>85</v>
       </c>
-      <c r="C87" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>88</v>
+      <c r="C87" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D87" s="13" t="s">
+        <v>56</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>89</v>
+        <v>42</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>11</v>
@@ -3089,24 +3180,25 @@
         <v>105000</v>
       </c>
       <c r="H87" s="2">
-        <v>165000</v>
-      </c>
-      <c r="I87" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="1"/>
+        <v>150000</v>
+      </c>
+      <c r="I87" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="88" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B88" s="6">
+      <c r="B88" s="5">
         <v>86</v>
       </c>
-      <c r="C88" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>88</v>
+      <c r="C88" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D88" s="13" t="s">
+        <v>56</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>89</v>
+        <v>42</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>11</v>
@@ -3115,24 +3207,25 @@
         <v>105000</v>
       </c>
       <c r="H88" s="2">
-        <v>165000</v>
-      </c>
-      <c r="I88" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="1"/>
+        <v>150000</v>
+      </c>
+      <c r="I88" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="89" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B89" s="6">
+      <c r="B89" s="5">
         <v>87</v>
       </c>
-      <c r="C89" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>88</v>
+      <c r="C89" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D89" s="13" t="s">
+        <v>56</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>89</v>
+        <v>42</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>11</v>
@@ -3141,24 +3234,25 @@
         <v>105000</v>
       </c>
       <c r="H89" s="2">
-        <v>165000</v>
-      </c>
-      <c r="I89" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="1"/>
+        <v>150000</v>
+      </c>
+      <c r="I89" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="90" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B90" s="6">
+      <c r="B90" s="5">
         <v>88</v>
       </c>
-      <c r="C90" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>44</v>
+      <c r="C90" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D90" s="13" t="s">
+        <v>34</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>90</v>
+        <v>57</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>11</v>
@@ -3167,76 +3261,79 @@
         <v>105000</v>
       </c>
       <c r="H90" s="2">
-        <v>165000</v>
-      </c>
-      <c r="I90" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="1"/>
+        <v>150000</v>
+      </c>
+      <c r="I90" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="91" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B91" s="6">
+      <c r="B91" s="5">
         <v>89</v>
       </c>
-      <c r="C91" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D91" s="1" t="s">
-        <v>44</v>
+      <c r="C91" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D91" s="13" t="s">
+        <v>34</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G91" s="2">
         <v>105000</v>
       </c>
       <c r="H91" s="2">
-        <v>165000</v>
-      </c>
-      <c r="I91" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="1"/>
+        <v>150000</v>
+      </c>
+      <c r="I91" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="92" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B92" s="6">
+      <c r="B92" s="5">
         <v>90</v>
       </c>
-      <c r="C92" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>37</v>
+      <c r="C92" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D92" s="13" t="s">
+        <v>9</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>92</v>
+        <v>58</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G92" s="2">
         <v>105000</v>
       </c>
       <c r="H92" s="2">
-        <v>165000</v>
-      </c>
-      <c r="I92" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="1"/>
+        <v>150000</v>
+      </c>
+      <c r="I92" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="93" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B93" s="6">
+      <c r="B93" s="5">
         <v>91</v>
       </c>
-      <c r="C93" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>93</v>
+      <c r="C93" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D93" s="13" t="s">
+        <v>59</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>94</v>
+        <v>60</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>11</v>
@@ -3245,24 +3342,25 @@
         <v>115000</v>
       </c>
       <c r="H93" s="2">
-        <v>175000</v>
-      </c>
-      <c r="I93" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="1"/>
+        <v>160000</v>
+      </c>
+      <c r="I93" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="94" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B94" s="6">
+      <c r="B94" s="5">
         <v>92</v>
       </c>
-      <c r="C94" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>93</v>
+      <c r="C94" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D94" s="13" t="s">
+        <v>59</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>94</v>
+        <v>60</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>11</v>
@@ -3271,24 +3369,25 @@
         <v>115000</v>
       </c>
       <c r="H94" s="2">
-        <v>175000</v>
-      </c>
-      <c r="I94" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="1"/>
+        <v>160000</v>
+      </c>
+      <c r="I94" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="95" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B95" s="6">
+      <c r="B95" s="5">
         <v>93</v>
       </c>
-      <c r="C95" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>93</v>
+      <c r="C95" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D95" s="13" t="s">
+        <v>59</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>94</v>
+        <v>60</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>11</v>
@@ -3297,24 +3396,25 @@
         <v>115000</v>
       </c>
       <c r="H95" s="2">
-        <v>175000</v>
-      </c>
-      <c r="I95" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="1"/>
+        <v>160000</v>
+      </c>
+      <c r="I95" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="96" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B96" s="6">
+      <c r="B96" s="5">
         <v>94</v>
       </c>
-      <c r="C96" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D96" s="1" t="s">
-        <v>93</v>
+      <c r="C96" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D96" s="13" t="s">
+        <v>59</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>94</v>
+        <v>60</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>11</v>
@@ -3323,76 +3423,79 @@
         <v>115000</v>
       </c>
       <c r="H96" s="2">
-        <v>175000</v>
-      </c>
-      <c r="I96" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="1"/>
+        <v>160000</v>
+      </c>
+      <c r="I96" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="97" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B97" s="6">
+      <c r="B97" s="5">
         <v>95</v>
       </c>
-      <c r="C97" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>93</v>
+      <c r="C97" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D97" s="13" t="s">
+        <v>59</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>94</v>
+        <v>60</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G97" s="2">
         <v>115000</v>
       </c>
       <c r="H97" s="2">
-        <v>175000</v>
-      </c>
-      <c r="I97" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="1"/>
+        <v>160000</v>
+      </c>
+      <c r="I97" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="98" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B98" s="6">
+      <c r="B98" s="5">
         <v>96</v>
       </c>
-      <c r="C98" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>76</v>
+      <c r="C98" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D98" s="13" t="s">
+        <v>50</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G98" s="2">
         <v>95000</v>
       </c>
       <c r="H98" s="2">
-        <v>155000</v>
-      </c>
-      <c r="I98" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="1"/>
+        <v>140000</v>
+      </c>
+      <c r="I98" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="99" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B99" s="6">
+      <c r="B99" s="5">
         <v>97</v>
       </c>
-      <c r="C99" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D99" s="1" t="s">
+      <c r="C99" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D99" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>11</v>
@@ -3401,24 +3504,25 @@
         <v>95000</v>
       </c>
       <c r="H99" s="2">
-        <v>155000</v>
-      </c>
-      <c r="I99" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="1"/>
+        <v>140000</v>
+      </c>
+      <c r="I99" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="100" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B100" s="6">
+      <c r="B100" s="5">
         <v>98</v>
       </c>
-      <c r="C100" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D100" s="1" t="s">
+      <c r="C100" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D100" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>11</v>
@@ -3427,24 +3531,25 @@
         <v>105000</v>
       </c>
       <c r="H100" s="2">
-        <v>165000</v>
-      </c>
-      <c r="I100" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="1"/>
+        <v>150000</v>
+      </c>
+      <c r="I100" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="101" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B101" s="6">
+      <c r="B101" s="5">
         <v>99</v>
       </c>
-      <c r="C101" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D101" s="1" t="s">
+      <c r="C101" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D101" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>11</v>
@@ -3453,128 +3558,133 @@
         <v>95000</v>
       </c>
       <c r="H101" s="2">
-        <v>155000</v>
-      </c>
-      <c r="I101" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="1"/>
+        <v>140000</v>
+      </c>
+      <c r="I101" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="102" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B102" s="6">
+      <c r="B102" s="5">
         <v>100</v>
       </c>
-      <c r="C102" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D102" s="1" t="s">
+      <c r="C102" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D102" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>85</v>
+        <v>30</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G102" s="2">
         <v>100000</v>
       </c>
       <c r="H102" s="2">
-        <v>160000</v>
-      </c>
-      <c r="I102" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="1"/>
+        <v>145000</v>
+      </c>
+      <c r="I102" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="103" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B103" s="6">
+      <c r="B103" s="5">
         <v>101</v>
       </c>
-      <c r="C103" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>37</v>
+      <c r="C103" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D103" s="13" t="s">
+        <v>9</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>92</v>
+        <v>58</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G103" s="2">
         <v>100000</v>
       </c>
       <c r="H103" s="2">
-        <v>160000</v>
-      </c>
-      <c r="I103" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="1"/>
+        <v>145000</v>
+      </c>
+      <c r="I103" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="104" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B104" s="6">
+      <c r="B104" s="5">
         <v>102</v>
       </c>
-      <c r="C104" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D104" s="1" t="s">
-        <v>37</v>
+      <c r="C104" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D104" s="13" t="s">
+        <v>9</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>92</v>
+        <v>58</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G104" s="2">
         <v>100000</v>
       </c>
       <c r="H104" s="2">
-        <v>160000</v>
-      </c>
-      <c r="I104" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="1"/>
+        <v>145000</v>
+      </c>
+      <c r="I104" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="105" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B105" s="6">
+      <c r="B105" s="5">
         <v>103</v>
       </c>
-      <c r="C105" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>37</v>
+      <c r="C105" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D105" s="13" t="s">
+        <v>9</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>92</v>
+        <v>58</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G105" s="2">
         <v>100000</v>
       </c>
       <c r="H105" s="2">
-        <v>160000</v>
-      </c>
-      <c r="I105" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="1"/>
+        <v>145000</v>
+      </c>
+      <c r="I105" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="106" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B106" s="6">
+      <c r="B106" s="5">
         <v>104</v>
       </c>
-      <c r="C106" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D106" s="1" t="s">
+      <c r="C106" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D106" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>11</v>
@@ -3583,50 +3693,52 @@
         <v>120000</v>
       </c>
       <c r="H106" s="2">
-        <v>180000</v>
-      </c>
-      <c r="I106" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="1"/>
+        <v>165000</v>
+      </c>
+      <c r="I106" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="107" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B107" s="6">
+      <c r="B107" s="5">
         <v>105</v>
       </c>
-      <c r="C107" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D107" s="1" t="s">
+      <c r="C107" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D107" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G107" s="2">
         <v>90000</v>
       </c>
       <c r="H107" s="2">
-        <v>150000</v>
-      </c>
-      <c r="I107" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="1"/>
+        <v>135000</v>
+      </c>
+      <c r="I107" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="108" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B108" s="6">
+      <c r="B108" s="5">
         <v>106</v>
       </c>
-      <c r="C108" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D108" s="1" t="s">
+      <c r="C108" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D108" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>57</v>
+        <v>100</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>11</v>
@@ -3635,76 +3747,79 @@
         <v>80000</v>
       </c>
       <c r="H108" s="2">
-        <v>140000</v>
-      </c>
-      <c r="I108" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="1"/>
+        <v>125000</v>
+      </c>
+      <c r="I108" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="109" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B109" s="6">
+      <c r="B109" s="5">
         <v>107</v>
       </c>
-      <c r="C109" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>100</v>
+      <c r="C109" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D109" s="13" t="s">
+        <v>61</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>101</v>
+        <v>62</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G109" s="2">
         <v>85000</v>
       </c>
       <c r="H109" s="2">
-        <v>145000</v>
-      </c>
-      <c r="I109" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="1"/>
+        <v>130000</v>
+      </c>
+      <c r="I109" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="110" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B110" s="6">
+      <c r="B110" s="5">
         <v>108</v>
       </c>
-      <c r="C110" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D110" s="1" t="s">
+      <c r="C110" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D110" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G110" s="2">
         <v>105000</v>
       </c>
       <c r="H110" s="2">
-        <v>165000</v>
-      </c>
-      <c r="I110" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="1"/>
+        <v>150000</v>
+      </c>
+      <c r="I110" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="111" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B111" s="6">
+      <c r="B111" s="5">
         <v>109</v>
       </c>
-      <c r="C111" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>69</v>
+      <c r="C111" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D111" s="13" t="s">
+        <v>97</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>11</v>
@@ -3713,102 +3828,106 @@
         <v>100000</v>
       </c>
       <c r="H111" s="2">
-        <v>160000</v>
-      </c>
-      <c r="I111" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="1"/>
+        <v>145000</v>
+      </c>
+      <c r="I111" s="5" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="112" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B112" s="6">
+      <c r="B112" s="5">
         <v>110</v>
       </c>
-      <c r="C112" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D112" s="1" t="s">
-        <v>69</v>
+      <c r="C112" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D112" s="13" t="s">
+        <v>97</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G112" s="2">
         <v>90000</v>
       </c>
       <c r="H112" s="2">
-        <v>150000</v>
-      </c>
-      <c r="I112" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="1"/>
+        <v>135000</v>
+      </c>
+      <c r="I112" s="5" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="113" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B113" s="6">
+      <c r="B113" s="5">
         <v>111</v>
       </c>
-      <c r="C113" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D113" s="1" t="s">
+      <c r="C113" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D113" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>57</v>
+        <v>100</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G113" s="2">
         <v>75000</v>
       </c>
       <c r="H113" s="2">
-        <v>135000</v>
-      </c>
-      <c r="I113" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="1"/>
+        <v>120000</v>
+      </c>
+      <c r="I113" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="114" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B114" s="6">
+      <c r="B114" s="5">
         <v>112</v>
       </c>
-      <c r="C114" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D114" s="1" t="s">
+      <c r="C114" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D114" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G114" s="2">
         <v>85000</v>
       </c>
       <c r="H114" s="2">
-        <v>145000</v>
-      </c>
-      <c r="I114" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="1"/>
+        <v>130000</v>
+      </c>
+      <c r="I114" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="115" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B115" s="6">
+      <c r="B115" s="5">
         <v>113</v>
       </c>
-      <c r="C115" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D115" s="1" t="s">
+      <c r="C115" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D115" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>11</v>
@@ -3817,24 +3936,25 @@
         <v>105000</v>
       </c>
       <c r="H115" s="2">
-        <v>165000</v>
-      </c>
-      <c r="I115" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="1"/>
+        <v>150000</v>
+      </c>
+      <c r="I115" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="116" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B116" s="6">
+      <c r="B116" s="5">
         <v>114</v>
       </c>
-      <c r="C116" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D116" s="1" t="s">
+      <c r="C116" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D116" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>11</v>
@@ -3843,128 +3963,133 @@
         <v>100000</v>
       </c>
       <c r="H116" s="2">
-        <v>160000</v>
-      </c>
-      <c r="I116" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="1"/>
+        <v>145000</v>
+      </c>
+      <c r="I116" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="117" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B117" s="6">
+      <c r="B117" s="5">
         <v>115</v>
       </c>
-      <c r="C117" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>44</v>
+      <c r="C117" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D117" s="13" t="s">
+        <v>34</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>45</v>
+        <v>121</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G117" s="2">
         <v>95000</v>
       </c>
       <c r="H117" s="2">
-        <v>155000</v>
-      </c>
-      <c r="I117" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="1"/>
+        <v>140000</v>
+      </c>
+      <c r="I117" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="118" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B118" s="6">
+      <c r="B118" s="5">
         <v>116</v>
       </c>
-      <c r="C118" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D118" s="1" t="s">
-        <v>106</v>
+      <c r="C118" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D118" s="13" t="s">
+        <v>64</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>106</v>
+        <v>64</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G118" s="2">
         <v>100000</v>
       </c>
       <c r="H118" s="2">
-        <v>160000</v>
-      </c>
-      <c r="I118" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="1"/>
+        <v>145000</v>
+      </c>
+      <c r="I118" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="119" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B119" s="6">
+      <c r="B119" s="5">
         <v>117</v>
       </c>
-      <c r="C119" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D119" s="1" t="s">
+      <c r="C119" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D119" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>107</v>
+        <v>51</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G119" s="2">
         <v>110000</v>
       </c>
       <c r="H119" s="2">
-        <v>170000</v>
-      </c>
-      <c r="I119" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="1"/>
+        <v>155000</v>
+      </c>
+      <c r="I119" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="120" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B120" s="6">
+      <c r="B120" s="5">
         <v>118</v>
       </c>
-      <c r="C120" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E120" s="1" t="s">
-        <v>108</v>
+      <c r="C120" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D120" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="E120" s="1">
+        <v>9060</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G120" s="2">
         <v>110000</v>
       </c>
       <c r="H120" s="2">
-        <v>170000</v>
-      </c>
-      <c r="I120" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="1"/>
+        <v>155000</v>
+      </c>
+      <c r="I120" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="121" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B121" s="6">
+      <c r="B121" s="5">
         <v>119</v>
       </c>
-      <c r="C121" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D121" s="1" t="s">
-        <v>56</v>
+      <c r="C121" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D121" s="13" t="s">
+        <v>40</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>109</v>
+        <v>65</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>11</v>
@@ -3973,50 +4098,52 @@
         <v>100000</v>
       </c>
       <c r="H121" s="2">
-        <v>160000</v>
-      </c>
-      <c r="I121" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="1"/>
+        <v>145000</v>
+      </c>
+      <c r="I121" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="122" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B122" s="6">
+      <c r="B122" s="5">
         <v>120</v>
       </c>
-      <c r="C122" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D122" s="1" t="s">
-        <v>56</v>
+      <c r="C122" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D122" s="13" t="s">
+        <v>34</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="G122" s="2">
-        <v>100000</v>
+        <v>95000</v>
       </c>
       <c r="H122" s="2">
-        <v>160000</v>
-      </c>
-      <c r="I122" s="6" t="s">
-        <v>132</v>
+        <f>G122+45000</f>
+        <v>140000</v>
+      </c>
+      <c r="I122" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="123" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B123" s="6">
+      <c r="B123" s="5">
         <v>121</v>
       </c>
-      <c r="C123" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D123" s="1" t="s">
-        <v>110</v>
+      <c r="C123" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D123" s="13" t="s">
+        <v>66</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>110</v>
+        <v>66</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>11</v>
@@ -4025,24 +4152,25 @@
         <v>95000</v>
       </c>
       <c r="H123" s="2">
-        <v>155000</v>
-      </c>
-      <c r="I123" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="1"/>
+        <v>140000</v>
+      </c>
+      <c r="I123" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="124" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B124" s="6">
+      <c r="B124" s="5">
         <v>122</v>
       </c>
-      <c r="C124" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D124" s="1" t="s">
-        <v>37</v>
+      <c r="C124" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D124" s="13" t="s">
+        <v>9</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>111</v>
+        <v>67</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>11</v>
@@ -4051,24 +4179,25 @@
         <v>100000</v>
       </c>
       <c r="H124" s="2">
-        <v>160000</v>
-      </c>
-      <c r="I124" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="1"/>
+        <v>145000</v>
+      </c>
+      <c r="I124" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="125" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B125" s="6">
+      <c r="B125" s="5">
         <v>123</v>
       </c>
-      <c r="C125" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D125" s="1" t="s">
-        <v>40</v>
+      <c r="C125" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D125" s="13" t="s">
+        <v>31</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>11</v>
@@ -4077,50 +4206,52 @@
         <v>95000</v>
       </c>
       <c r="H125" s="2">
-        <v>145000</v>
-      </c>
-      <c r="I125" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="1"/>
+        <v>140000</v>
+      </c>
+      <c r="I125" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="126" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B126" s="6">
+      <c r="B126" s="5">
         <v>124</v>
       </c>
-      <c r="C126" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D126" s="1" t="s">
-        <v>113</v>
+      <c r="C126" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D126" s="13" t="s">
+        <v>68</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>113</v>
+        <v>68</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G126" s="2">
         <v>90000</v>
       </c>
       <c r="H126" s="2">
-        <v>150000</v>
-      </c>
-      <c r="I126" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="1"/>
+        <v>135000</v>
+      </c>
+      <c r="I126" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="127" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B127" s="6">
+      <c r="B127" s="5">
         <v>125</v>
       </c>
-      <c r="C127" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D127" s="1" t="s">
+      <c r="C127" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D127" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>114</v>
+        <v>69</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>11</v>
@@ -4129,76 +4260,79 @@
         <v>105000</v>
       </c>
       <c r="H127" s="2">
-        <v>165000</v>
-      </c>
-      <c r="I127" s="6" t="s">
-        <v>132</v>
+        <f t="shared" si="1"/>
+        <v>150000</v>
+      </c>
+      <c r="I127" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="128" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B128" s="7">
+      <c r="B128" s="6">
         <v>126</v>
       </c>
-      <c r="C128" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D128" s="1" t="s">
-        <v>21</v>
+      <c r="C128" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D128" s="13" t="s">
+        <v>18</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G128" s="2">
         <v>85000</v>
       </c>
       <c r="H128" s="2">
-        <v>145000</v>
-      </c>
-      <c r="I128" s="7" t="s">
-        <v>132</v>
+        <f t="shared" si="1"/>
+        <v>130000</v>
+      </c>
+      <c r="I128" s="6" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="129" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B129" s="7">
+      <c r="B129" s="6">
         <v>127</v>
       </c>
-      <c r="C129" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>21</v>
+      <c r="C129" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D129" s="13" t="s">
+        <v>18</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G129" s="2">
         <v>85000</v>
       </c>
       <c r="H129" s="2">
-        <v>145000</v>
-      </c>
-      <c r="I129" s="7" t="s">
-        <v>132</v>
+        <f t="shared" si="1"/>
+        <v>130000</v>
+      </c>
+      <c r="I129" s="6" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="130" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B130" s="7">
+      <c r="B130" s="6">
         <v>128</v>
       </c>
-      <c r="C130" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D130" s="1" t="s">
+      <c r="C130" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D130" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>11</v>
@@ -4207,24 +4341,25 @@
         <v>90000</v>
       </c>
       <c r="H130" s="2">
-        <v>150000</v>
-      </c>
-      <c r="I130" s="7" t="s">
-        <v>132</v>
+        <f t="shared" si="1"/>
+        <v>135000</v>
+      </c>
+      <c r="I130" s="6" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="131" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B131" s="7">
+      <c r="B131" s="6">
         <v>129</v>
       </c>
-      <c r="C131" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D131" s="1" t="s">
+      <c r="C131" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D131" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>11</v>
@@ -4233,24 +4368,25 @@
         <v>90000</v>
       </c>
       <c r="H131" s="2">
-        <v>150000</v>
-      </c>
-      <c r="I131" s="7" t="s">
-        <v>132</v>
+        <f t="shared" si="1"/>
+        <v>135000</v>
+      </c>
+      <c r="I131" s="6" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="132" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B132" s="7">
+      <c r="B132" s="6">
         <v>130</v>
       </c>
-      <c r="C132" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D132" s="1" t="s">
+      <c r="C132" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D132" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>115</v>
+        <v>70</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>11</v>
@@ -4259,24 +4395,25 @@
         <v>105000</v>
       </c>
       <c r="H132" s="2">
-        <v>165000</v>
-      </c>
-      <c r="I132" s="7" t="s">
-        <v>132</v>
+        <f t="shared" ref="H132:H179" si="2">G132+45000</f>
+        <v>150000</v>
+      </c>
+      <c r="I132" s="6" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="133" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B133" s="7">
+      <c r="B133" s="6">
         <v>131</v>
       </c>
-      <c r="C133" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D133" s="1" t="s">
+      <c r="C133" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D133" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>115</v>
+        <v>70</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>11</v>
@@ -4285,24 +4422,25 @@
         <v>105000</v>
       </c>
       <c r="H133" s="2">
-        <v>165000</v>
-      </c>
-      <c r="I133" s="7" t="s">
+        <f t="shared" si="2"/>
+        <v>150000</v>
+      </c>
+      <c r="I133" s="6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="134" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B134" s="6">
         <v>132</v>
       </c>
-    </row>
-    <row r="134" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B134" s="7">
-        <v>132</v>
-      </c>
-      <c r="C134" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D134" s="1" t="s">
+      <c r="C134" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D134" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>116</v>
+        <v>71</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>11</v>
@@ -4311,24 +4449,25 @@
         <v>100000</v>
       </c>
       <c r="H134" s="2">
-        <v>160000</v>
-      </c>
-      <c r="I134" s="7" t="s">
-        <v>132</v>
+        <f t="shared" si="2"/>
+        <v>145000</v>
+      </c>
+      <c r="I134" s="6" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="135" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B135" s="7">
+      <c r="B135" s="6">
         <v>133</v>
       </c>
-      <c r="C135" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D135" s="1" t="s">
+      <c r="C135" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D135" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>116</v>
+        <v>71</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>11</v>
@@ -4337,24 +4476,25 @@
         <v>100000</v>
       </c>
       <c r="H135" s="2">
-        <v>160000</v>
-      </c>
-      <c r="I135" s="7" t="s">
-        <v>132</v>
+        <f t="shared" si="2"/>
+        <v>145000</v>
+      </c>
+      <c r="I135" s="6" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="136" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B136" s="7">
+      <c r="B136" s="6">
         <v>134</v>
       </c>
-      <c r="C136" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D136" s="1" t="s">
-        <v>117</v>
+      <c r="C136" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D136" s="13" t="s">
+        <v>72</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>118</v>
+        <v>74</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>11</v>
@@ -4363,24 +4503,25 @@
         <v>115000</v>
       </c>
       <c r="H136" s="2">
-        <v>175000</v>
-      </c>
-      <c r="I136" s="7" t="s">
-        <v>132</v>
+        <f t="shared" si="2"/>
+        <v>160000</v>
+      </c>
+      <c r="I136" s="6" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="137" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B137" s="7">
+      <c r="B137" s="6">
         <v>135</v>
       </c>
-      <c r="C137" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D137" s="1" t="s">
-        <v>117</v>
+      <c r="C137" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D137" s="13" t="s">
+        <v>72</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>118</v>
+        <v>74</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>11</v>
@@ -4389,24 +4530,25 @@
         <v>115000</v>
       </c>
       <c r="H137" s="2">
-        <v>175000</v>
-      </c>
-      <c r="I137" s="7" t="s">
-        <v>132</v>
+        <f t="shared" si="2"/>
+        <v>160000</v>
+      </c>
+      <c r="I137" s="6" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="138" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B138" s="7">
+      <c r="B138" s="6">
         <v>136</v>
       </c>
-      <c r="C138" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D138" s="1" t="s">
+      <c r="C138" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D138" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>11</v>
@@ -4415,154 +4557,160 @@
         <v>100000</v>
       </c>
       <c r="H138" s="2">
-        <v>160000</v>
-      </c>
-      <c r="I138" s="7" t="s">
-        <v>132</v>
+        <f t="shared" si="2"/>
+        <v>145000</v>
+      </c>
+      <c r="I138" s="6" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="139" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B139" s="7">
+      <c r="B139" s="6">
         <v>137</v>
       </c>
-      <c r="C139" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>119</v>
+      <c r="C139" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D139" s="13" t="s">
+        <v>9</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G139" s="2">
         <v>105000</v>
       </c>
       <c r="H139" s="2">
-        <v>165000</v>
-      </c>
-      <c r="I139" s="7" t="s">
-        <v>132</v>
+        <f t="shared" si="2"/>
+        <v>150000</v>
+      </c>
+      <c r="I139" s="6" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="140" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B140" s="7">
+      <c r="B140" s="6">
         <v>138</v>
       </c>
-      <c r="C140" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D140" s="1" t="s">
+      <c r="C140" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D140" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G140" s="2">
         <v>110000</v>
       </c>
       <c r="H140" s="2">
-        <v>170000</v>
-      </c>
-      <c r="I140" s="7" t="s">
-        <v>132</v>
+        <f t="shared" si="2"/>
+        <v>155000</v>
+      </c>
+      <c r="I140" s="6" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="141" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B141" s="7">
+      <c r="B141" s="6">
         <v>139</v>
       </c>
-      <c r="C141" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D141" s="1" t="s">
+      <c r="C141" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D141" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G141" s="2">
         <v>110000</v>
       </c>
       <c r="H141" s="2">
-        <v>170000</v>
-      </c>
-      <c r="I141" s="7" t="s">
-        <v>132</v>
+        <f t="shared" si="2"/>
+        <v>155000</v>
+      </c>
+      <c r="I141" s="6" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="142" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B142" s="7">
+      <c r="B142" s="6">
         <v>140</v>
       </c>
-      <c r="C142" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D142" s="1" t="s">
+      <c r="C142" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D142" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G142" s="2">
         <v>110000</v>
       </c>
       <c r="H142" s="2">
-        <v>170000</v>
-      </c>
-      <c r="I142" s="7" t="s">
-        <v>132</v>
+        <f t="shared" si="2"/>
+        <v>155000</v>
+      </c>
+      <c r="I142" s="6" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="143" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B143" s="7">
+      <c r="B143" s="6">
         <v>141</v>
       </c>
-      <c r="C143" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D143" s="1" t="s">
+      <c r="C143" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D143" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G143" s="2">
         <v>110000</v>
       </c>
       <c r="H143" s="2">
-        <v>170000</v>
-      </c>
-      <c r="I143" s="7" t="s">
-        <v>132</v>
+        <f t="shared" si="2"/>
+        <v>155000</v>
+      </c>
+      <c r="I143" s="6" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="144" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B144" s="7">
+      <c r="B144" s="6">
         <v>142</v>
       </c>
-      <c r="C144" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D144" s="1" t="s">
+      <c r="C144" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D144" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>121</v>
+        <v>73</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>11</v>
@@ -4571,24 +4719,25 @@
         <v>90000</v>
       </c>
       <c r="H144" s="2">
-        <v>150000</v>
-      </c>
-      <c r="I144" s="7" t="s">
-        <v>132</v>
+        <f t="shared" si="2"/>
+        <v>135000</v>
+      </c>
+      <c r="I144" s="6" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="145" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B145" s="7">
+      <c r="B145" s="6">
         <v>143</v>
       </c>
-      <c r="C145" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D145" s="1" t="s">
+      <c r="C145" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D145" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>121</v>
+        <v>73</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>11</v>
@@ -4597,50 +4746,52 @@
         <v>90000</v>
       </c>
       <c r="H145" s="2">
-        <v>150000</v>
-      </c>
-      <c r="I145" s="7" t="s">
-        <v>132</v>
+        <f t="shared" si="2"/>
+        <v>135000</v>
+      </c>
+      <c r="I145" s="6" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="146" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B146" s="7">
+      <c r="B146" s="6">
         <v>144</v>
       </c>
-      <c r="C146" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D146" s="1" t="s">
+      <c r="C146" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D146" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>122</v>
+        <v>74</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G146" s="2">
         <v>85000</v>
       </c>
       <c r="H146" s="2">
-        <v>145000</v>
-      </c>
-      <c r="I146" s="7" t="s">
-        <v>132</v>
+        <f t="shared" si="2"/>
+        <v>130000</v>
+      </c>
+      <c r="I146" s="6" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="147" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B147" s="7">
+      <c r="B147" s="6">
         <v>145</v>
       </c>
-      <c r="C147" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D147" s="1" t="s">
-        <v>100</v>
+      <c r="C147" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D147" s="13" t="s">
+        <v>61</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>123</v>
+        <v>75</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>11</v>
@@ -4649,24 +4800,25 @@
         <v>85000</v>
       </c>
       <c r="H147" s="2">
-        <v>145000</v>
-      </c>
-      <c r="I147" s="7" t="s">
-        <v>132</v>
+        <f t="shared" si="2"/>
+        <v>130000</v>
+      </c>
+      <c r="I147" s="6" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="148" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B148" s="7">
+      <c r="B148" s="6">
         <v>146</v>
       </c>
-      <c r="C148" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D148" s="1" t="s">
-        <v>100</v>
+      <c r="C148" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D148" s="13" t="s">
+        <v>61</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>123</v>
+        <v>75</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>11</v>
@@ -4675,24 +4827,25 @@
         <v>85000</v>
       </c>
       <c r="H148" s="2">
-        <v>145000</v>
-      </c>
-      <c r="I148" s="7" t="s">
-        <v>132</v>
+        <f t="shared" si="2"/>
+        <v>130000</v>
+      </c>
+      <c r="I148" s="6" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="149" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B149" s="7">
+      <c r="B149" s="6">
         <v>147</v>
       </c>
-      <c r="C149" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D149" s="1" t="s">
-        <v>31</v>
+      <c r="C149" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D149" s="13" t="s">
+        <v>27</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>124</v>
+        <v>76</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>11</v>
@@ -4701,24 +4854,25 @@
         <v>80000</v>
       </c>
       <c r="H149" s="2">
-        <v>140000</v>
-      </c>
-      <c r="I149" s="7" t="s">
-        <v>132</v>
+        <f>G149+45000</f>
+        <v>125000</v>
+      </c>
+      <c r="I149" s="6" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="150" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B150" s="7">
+      <c r="B150" s="6">
         <v>148</v>
       </c>
-      <c r="C150" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D150" s="1" t="s">
-        <v>31</v>
+      <c r="C150" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D150" s="13" t="s">
+        <v>27</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>124</v>
+        <v>76</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>11</v>
@@ -4727,128 +4881,133 @@
         <v>80000</v>
       </c>
       <c r="H150" s="2">
-        <v>140000</v>
-      </c>
-      <c r="I150" s="7" t="s">
-        <v>132</v>
+        <f t="shared" si="2"/>
+        <v>125000</v>
+      </c>
+      <c r="I150" s="6" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="151" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B151" s="7">
+      <c r="B151" s="6">
         <v>149</v>
       </c>
-      <c r="C151" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D151" s="1" t="s">
-        <v>59</v>
+      <c r="C151" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D151" s="13" t="s">
+        <v>41</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G151" s="2">
         <v>110000</v>
       </c>
       <c r="H151" s="2">
-        <v>170000</v>
-      </c>
-      <c r="I151" s="7" t="s">
-        <v>132</v>
+        <f t="shared" si="2"/>
+        <v>155000</v>
+      </c>
+      <c r="I151" s="6" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="152" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B152" s="7">
+      <c r="B152" s="6">
         <v>150</v>
       </c>
-      <c r="C152" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D152" s="1" t="s">
-        <v>76</v>
+      <c r="C152" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D152" s="13" t="s">
+        <v>50</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G152" s="2">
         <v>95000</v>
       </c>
       <c r="H152" s="2">
-        <v>155000</v>
-      </c>
-      <c r="I152" s="7" t="s">
-        <v>132</v>
+        <f t="shared" si="2"/>
+        <v>140000</v>
+      </c>
+      <c r="I152" s="6" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="153" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B153" s="7">
+      <c r="B153" s="6">
         <v>151</v>
       </c>
-      <c r="C153" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D153" s="1" t="s">
+      <c r="C153" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D153" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>126</v>
+        <v>78</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G153" s="2">
         <v>105000</v>
       </c>
       <c r="H153" s="2">
-        <v>165000</v>
-      </c>
-      <c r="I153" s="7" t="s">
-        <v>132</v>
+        <f t="shared" si="2"/>
+        <v>150000</v>
+      </c>
+      <c r="I153" s="6" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="154" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B154" s="7">
+      <c r="B154" s="6">
         <v>152</v>
       </c>
-      <c r="C154" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D154" s="1" t="s">
+      <c r="C154" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D154" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>127</v>
+        <v>79</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G154" s="2">
         <v>90000</v>
       </c>
       <c r="H154" s="2">
-        <v>150000</v>
-      </c>
-      <c r="I154" s="7" t="s">
-        <v>132</v>
+        <f t="shared" si="2"/>
+        <v>135000</v>
+      </c>
+      <c r="I154" s="6" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="155" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B155" s="7">
+      <c r="B155" s="6">
         <v>153</v>
       </c>
-      <c r="C155" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D155" s="1" t="s">
-        <v>37</v>
+      <c r="C155" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D155" s="13" t="s">
+        <v>9</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>128</v>
+        <v>80</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>11</v>
@@ -4857,24 +5016,25 @@
         <v>95000</v>
       </c>
       <c r="H155" s="2">
-        <v>155000</v>
-      </c>
-      <c r="I155" s="7" t="s">
-        <v>132</v>
+        <f t="shared" si="2"/>
+        <v>140000</v>
+      </c>
+      <c r="I155" s="6" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="156" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B156" s="7">
+      <c r="B156" s="6">
         <v>154</v>
       </c>
-      <c r="C156" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D156" s="1" t="s">
+      <c r="C156" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D156" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>129</v>
+        <v>81</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>11</v>
@@ -4883,24 +5043,25 @@
         <v>105000</v>
       </c>
       <c r="H156" s="2">
-        <v>165000</v>
-      </c>
-      <c r="I156" s="7" t="s">
-        <v>132</v>
+        <f t="shared" si="2"/>
+        <v>150000</v>
+      </c>
+      <c r="I156" s="6" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="157" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B157" s="7">
+      <c r="B157" s="6">
         <v>155</v>
       </c>
-      <c r="C157" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D157" s="1" t="s">
+      <c r="C157" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D157" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>129</v>
+        <v>81</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>11</v>
@@ -4909,24 +5070,25 @@
         <v>105000</v>
       </c>
       <c r="H157" s="2">
-        <v>165000</v>
-      </c>
-      <c r="I157" s="7" t="s">
-        <v>132</v>
+        <f t="shared" si="2"/>
+        <v>150000</v>
+      </c>
+      <c r="I157" s="6" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="158" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B158" s="7">
+      <c r="B158" s="6">
         <v>156</v>
       </c>
-      <c r="C158" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D158" s="1" t="s">
-        <v>40</v>
+      <c r="C158" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D158" s="13" t="s">
+        <v>31</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>11</v>
@@ -4935,79 +5097,621 @@
         <v>85000</v>
       </c>
       <c r="H158" s="2">
+        <f t="shared" si="2"/>
+        <v>130000</v>
+      </c>
+      <c r="I158" s="6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="159" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B159" s="8">
+        <v>157</v>
+      </c>
+      <c r="C159" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D159" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="E159" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="F159" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G159" s="10">
+        <v>100000</v>
+      </c>
+      <c r="H159" s="2">
+        <f t="shared" si="2"/>
         <v>145000</v>
       </c>
-      <c r="I158" s="7" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="159" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B159" s="7">
-        <v>157</v>
-      </c>
-      <c r="C159" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D159" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E159" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="F159" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G159" s="2">
+      <c r="I159" s="8" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="160" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B160" s="6">
+        <v>158</v>
+      </c>
+      <c r="C160" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D160" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E160" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F160" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G160" s="2">
         <v>100000</v>
       </c>
-      <c r="H159" s="2">
-        <v>160000</v>
-      </c>
-      <c r="I159" s="7" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="160" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B160" s="7"/>
-      <c r="C160" s="6"/>
-      <c r="D160" s="1"/>
-      <c r="E160" s="1"/>
-      <c r="F160" s="1"/>
-      <c r="G160" s="2"/>
-      <c r="H160" s="2"/>
-      <c r="I160" s="7"/>
+      <c r="H160" s="2">
+        <f t="shared" si="2"/>
+        <v>145000</v>
+      </c>
+      <c r="I160" s="6"/>
     </row>
     <row r="161" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B161" s="7"/>
-      <c r="C161" s="6"/>
-      <c r="D161" s="1"/>
-      <c r="E161" s="1"/>
-      <c r="F161" s="1"/>
-      <c r="G161" s="2"/>
-      <c r="H161" s="2"/>
-      <c r="I161" s="7"/>
+      <c r="B161" s="6">
+        <v>159</v>
+      </c>
+      <c r="C161" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D161" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E161" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F161" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G161" s="2">
+        <v>100000</v>
+      </c>
+      <c r="H161" s="2">
+        <f t="shared" si="2"/>
+        <v>145000</v>
+      </c>
+      <c r="I161" s="6"/>
     </row>
     <row r="162" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B162" s="7"/>
-      <c r="C162" s="6"/>
-      <c r="D162" s="1"/>
-      <c r="E162" s="1"/>
-      <c r="F162" s="1"/>
-      <c r="G162" s="2"/>
-      <c r="H162" s="2"/>
-      <c r="I162" s="7"/>
+      <c r="B162" s="6">
+        <v>160</v>
+      </c>
+      <c r="C162" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D162" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="E162" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F162" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G162" s="2">
+        <v>85000</v>
+      </c>
+      <c r="H162" s="2">
+        <f t="shared" si="2"/>
+        <v>130000</v>
+      </c>
+      <c r="I162" s="6"/>
     </row>
     <row r="163" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B163" s="8"/>
-      <c r="C163" s="8"/>
-      <c r="D163" s="3"/>
-      <c r="E163" s="3"/>
-      <c r="F163" s="3"/>
-      <c r="G163" s="4"/>
-      <c r="H163" s="4"/>
-      <c r="I163" s="8"/>
+      <c r="B163" s="6">
+        <v>161</v>
+      </c>
+      <c r="C163" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D163" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="E163" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F163" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G163" s="2">
+        <v>100000</v>
+      </c>
+      <c r="H163" s="2">
+        <f t="shared" si="2"/>
+        <v>145000</v>
+      </c>
+      <c r="I163" s="6"/>
+    </row>
+    <row r="164" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B164" s="6">
+        <v>162</v>
+      </c>
+      <c r="C164" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D164" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="E164" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F164" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G164" s="2">
+        <v>100000</v>
+      </c>
+      <c r="H164" s="2">
+        <f t="shared" si="2"/>
+        <v>145000</v>
+      </c>
+      <c r="I164" s="6"/>
+    </row>
+    <row r="165" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B165" s="6">
+        <v>163</v>
+      </c>
+      <c r="C165" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D165" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E165" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F165" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G165" s="2">
+        <v>95000</v>
+      </c>
+      <c r="H165" s="2">
+        <f t="shared" si="2"/>
+        <v>140000</v>
+      </c>
+      <c r="I165" s="6"/>
+    </row>
+    <row r="166" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B166" s="6">
+        <v>164</v>
+      </c>
+      <c r="C166" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D166" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E166" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F166" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G166" s="2">
+        <v>105000</v>
+      </c>
+      <c r="H166" s="2">
+        <f t="shared" si="2"/>
+        <v>150000</v>
+      </c>
+      <c r="I166" s="6"/>
+    </row>
+    <row r="167" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B167" s="6">
+        <v>165</v>
+      </c>
+      <c r="C167" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D167" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="E167" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F167" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G167" s="2">
+        <v>110000</v>
+      </c>
+      <c r="H167" s="2">
+        <f t="shared" si="2"/>
+        <v>155000</v>
+      </c>
+      <c r="I167" s="6"/>
+    </row>
+    <row r="168" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B168" s="6">
+        <v>166</v>
+      </c>
+      <c r="C168" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D168" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="E168" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F168" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G168" s="2">
+        <v>110000</v>
+      </c>
+      <c r="H168" s="2">
+        <f t="shared" si="2"/>
+        <v>155000</v>
+      </c>
+      <c r="I168" s="6"/>
+    </row>
+    <row r="169" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B169" s="6">
+        <v>167</v>
+      </c>
+      <c r="C169" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D169" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="E169" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F169" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G169" s="2">
+        <v>110000</v>
+      </c>
+      <c r="H169" s="2">
+        <f t="shared" si="2"/>
+        <v>155000</v>
+      </c>
+      <c r="I169" s="6"/>
+    </row>
+    <row r="170" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B170" s="6">
+        <v>168</v>
+      </c>
+      <c r="C170" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D170" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="E170" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F170" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G170" s="2">
+        <v>105000</v>
+      </c>
+      <c r="H170" s="2">
+        <f t="shared" si="2"/>
+        <v>150000</v>
+      </c>
+      <c r="I170" s="6"/>
+    </row>
+    <row r="171" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B171" s="6">
+        <v>169</v>
+      </c>
+      <c r="C171" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D171" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="E171" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F171" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G171" s="2">
+        <v>105000</v>
+      </c>
+      <c r="H171" s="2">
+        <f t="shared" si="2"/>
+        <v>150000</v>
+      </c>
+      <c r="I171" s="6"/>
+    </row>
+    <row r="172" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B172" s="6">
+        <v>170</v>
+      </c>
+      <c r="C172" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D172" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="E172" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F172" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G172" s="2">
+        <v>105000</v>
+      </c>
+      <c r="H172" s="2">
+        <f t="shared" si="2"/>
+        <v>150000</v>
+      </c>
+      <c r="I172" s="6"/>
+    </row>
+    <row r="173" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B173" s="6">
+        <v>171</v>
+      </c>
+      <c r="C173" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D173" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E173" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F173" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G173" s="2">
+        <v>95000</v>
+      </c>
+      <c r="H173" s="2">
+        <f t="shared" si="2"/>
+        <v>140000</v>
+      </c>
+      <c r="I173" s="6"/>
+    </row>
+    <row r="174" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B174" s="6">
+        <v>172</v>
+      </c>
+      <c r="C174" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D174" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E174" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F174" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G174" s="2">
+        <v>95000</v>
+      </c>
+      <c r="H174" s="2">
+        <f t="shared" si="2"/>
+        <v>140000</v>
+      </c>
+      <c r="I174" s="6"/>
+    </row>
+    <row r="175" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B175" s="6">
+        <v>173</v>
+      </c>
+      <c r="C175" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D175" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E175" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F175" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G175" s="2">
+        <v>100000</v>
+      </c>
+      <c r="H175" s="2">
+        <f t="shared" si="2"/>
+        <v>145000</v>
+      </c>
+      <c r="I175" s="6"/>
+    </row>
+    <row r="176" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B176" s="6">
+        <v>174</v>
+      </c>
+      <c r="C176" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D176" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E176" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F176" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G176" s="2">
+        <v>100000</v>
+      </c>
+      <c r="H176" s="2">
+        <f t="shared" si="2"/>
+        <v>145000</v>
+      </c>
+      <c r="I176" s="6"/>
+    </row>
+    <row r="177" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B177" s="6">
+        <v>175</v>
+      </c>
+      <c r="C177" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D177" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E177" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F177" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G177" s="2">
+        <v>110000</v>
+      </c>
+      <c r="H177" s="2">
+        <f t="shared" si="2"/>
+        <v>155000</v>
+      </c>
+      <c r="I177" s="6"/>
+    </row>
+    <row r="178" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B178" s="6">
+        <v>176</v>
+      </c>
+      <c r="C178" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D178" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="E178" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F178" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G178" s="2">
+        <v>100000</v>
+      </c>
+      <c r="H178" s="2">
+        <f t="shared" si="2"/>
+        <v>145000</v>
+      </c>
+      <c r="I178" s="6"/>
+    </row>
+    <row r="179" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B179" s="6"/>
+      <c r="C179" s="5"/>
+      <c r="D179" s="13"/>
+      <c r="E179" s="1"/>
+      <c r="F179" s="1"/>
+      <c r="G179" s="2"/>
+      <c r="H179" s="2"/>
+      <c r="I179" s="6"/>
+    </row>
+    <row r="180" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B180" s="6"/>
+      <c r="C180" s="5"/>
+      <c r="D180" s="13"/>
+      <c r="E180" s="1"/>
+      <c r="F180" s="1"/>
+      <c r="G180" s="2"/>
+      <c r="H180" s="2"/>
+      <c r="I180" s="6"/>
+    </row>
+    <row r="181" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B181" s="6"/>
+      <c r="C181" s="5"/>
+      <c r="D181" s="13"/>
+      <c r="E181" s="1"/>
+      <c r="F181" s="1"/>
+      <c r="G181" s="2"/>
+      <c r="H181" s="2"/>
+      <c r="I181" s="6"/>
+    </row>
+    <row r="182" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B182" s="6"/>
+      <c r="C182" s="5"/>
+      <c r="D182" s="13"/>
+      <c r="E182" s="1"/>
+      <c r="F182" s="1"/>
+      <c r="G182" s="2"/>
+      <c r="H182" s="2"/>
+      <c r="I182" s="6"/>
+    </row>
+    <row r="183" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B183" s="6"/>
+      <c r="C183" s="5"/>
+      <c r="D183" s="13"/>
+      <c r="E183" s="1"/>
+      <c r="F183" s="1"/>
+      <c r="G183" s="2"/>
+      <c r="H183" s="2"/>
+      <c r="I183" s="6"/>
+    </row>
+    <row r="184" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B184" s="6"/>
+      <c r="C184" s="5"/>
+      <c r="D184" s="13"/>
+      <c r="E184" s="1"/>
+      <c r="F184" s="1"/>
+      <c r="G184" s="2"/>
+      <c r="H184" s="2"/>
+      <c r="I184" s="6"/>
+    </row>
+    <row r="185" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B185" s="6"/>
+      <c r="C185" s="5"/>
+      <c r="D185" s="13"/>
+      <c r="E185" s="1"/>
+      <c r="F185" s="1"/>
+      <c r="G185" s="2"/>
+      <c r="H185" s="2"/>
+      <c r="I185" s="6"/>
+    </row>
+    <row r="186" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B186" s="6"/>
+      <c r="C186" s="5"/>
+      <c r="D186" s="13"/>
+      <c r="E186" s="1"/>
+      <c r="F186" s="1"/>
+      <c r="G186" s="2"/>
+      <c r="H186" s="2"/>
+      <c r="I186" s="6"/>
+    </row>
+    <row r="187" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B187" s="6"/>
+      <c r="C187" s="5"/>
+      <c r="D187" s="13"/>
+      <c r="E187" s="1"/>
+      <c r="F187" s="1"/>
+      <c r="G187" s="2"/>
+      <c r="H187" s="2"/>
+      <c r="I187" s="6"/>
+    </row>
+    <row r="188" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B188" s="6"/>
+      <c r="C188" s="5"/>
+      <c r="D188" s="13"/>
+      <c r="E188" s="1"/>
+      <c r="F188" s="1"/>
+      <c r="G188" s="2"/>
+      <c r="H188" s="2"/>
+      <c r="I188" s="6"/>
+    </row>
+    <row r="189" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="G189" s="3"/>
+      <c r="H189" s="3"/>
     </row>
   </sheetData>
+  <autoFilter ref="B2:I180" xr:uid="{F75DB620-AF17-408B-81D4-431B9D551CF9}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/assets/LISTA ZAPATILLAS.xlsx
+++ b/assets/LISTA ZAPATILLAS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30110"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d8bfe2c87cad12b0/IA/MILENASHOES/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{E0C42F5F-A3E4-4F22-AD40-E0497D996882}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15064101-52DF-41C6-93C1-27C93922BA61}"/>
+  <xr:revisionPtr revIDLastSave="79" documentId="13_ncr:1_{E0C42F5F-A3E4-4F22-AD40-E0497D996882}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BCA1ACB4-A517-45A0-B9B2-5B5BEBAE0C1E}"/>
   <bookViews>
     <workbookView xWindow="1545" yWindow="1125" windowWidth="15570" windowHeight="13710" xr2:uid="{B7A6A16F-7A19-4864-8939-1CF29A8D65F8}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">INVENTARIO!$B$2:$I$180</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -30,17 +30,16 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="867" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="903" uniqueCount="134">
   <si>
     <t xml:space="preserve">NUMERO </t>
   </si>
@@ -63,27 +62,39 @@
     <t>VENTA</t>
   </si>
   <si>
+    <t>DISPONIBLE</t>
+  </si>
+  <si>
     <t>H</t>
   </si>
   <si>
+    <t>NIKE</t>
+  </si>
+  <si>
+    <t>AF1 SAIL RIPSTOP</t>
+  </si>
+  <si>
+    <t>EU 40 AL 44</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
     <t>M</t>
   </si>
   <si>
-    <t>NIKE</t>
-  </si>
-  <si>
-    <t>AF1 SAIL RIPSTOP</t>
-  </si>
-  <si>
-    <t>EU 40 AL 44</t>
-  </si>
-  <si>
     <t>ADIDAS</t>
   </si>
   <si>
+    <t>BOUNCE</t>
+  </si>
+  <si>
     <t>EU 36 AL 40</t>
   </si>
   <si>
+    <t>P7000</t>
+  </si>
+  <si>
     <t>EU 36 AL 39</t>
   </si>
   <si>
@@ -96,117 +107,186 @@
     <t>EU 36 AL 42</t>
   </si>
   <si>
+    <t>TRAIL</t>
+  </si>
+  <si>
     <t>SKECHERS</t>
   </si>
   <si>
+    <t>M Y H</t>
+  </si>
+  <si>
+    <t>ADIZERO</t>
+  </si>
+  <si>
+    <t>EU 36 AL 44</t>
+  </si>
+  <si>
+    <t>ASICS</t>
+  </si>
+  <si>
+    <t>ASICS RUN</t>
+  </si>
+  <si>
+    <t>P-7000</t>
+  </si>
+  <si>
+    <t>NEW BALANCE</t>
+  </si>
+  <si>
+    <t>ARMANI</t>
+  </si>
+  <si>
+    <t>ASCIS RUN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NEW BALANCE </t>
+  </si>
+  <si>
+    <t>RUN</t>
+  </si>
+  <si>
+    <t>COACH</t>
+  </si>
+  <si>
+    <t>JORDAN RETRO 1 LOW</t>
+  </si>
+  <si>
+    <t>SAMBA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REEBOK </t>
+  </si>
+  <si>
+    <t>CLUB</t>
+  </si>
+  <si>
+    <t>LACOSTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LACOSTE ALPACINO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VANS </t>
+  </si>
+  <si>
+    <t>HYLANE</t>
+  </si>
+  <si>
+    <t>KNU</t>
+  </si>
+  <si>
+    <t>FLOATZIG</t>
+  </si>
+  <si>
+    <t>ZOOM PEGASUS</t>
+  </si>
+  <si>
+    <t>SB PARRA</t>
+  </si>
+  <si>
+    <t>SB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LACOSTE </t>
+  </si>
+  <si>
+    <t>SB SUPREME</t>
+  </si>
+  <si>
+    <t>AF1 SUPREME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NIKE </t>
+  </si>
+  <si>
+    <t>AF1</t>
+  </si>
+  <si>
+    <t>JORDAN RETRO 1</t>
+  </si>
+  <si>
+    <t>LOUIS VUITTON</t>
+  </si>
+  <si>
+    <t>SKATE</t>
+  </si>
+  <si>
+    <t>P-6000</t>
+  </si>
+  <si>
+    <t>P-6001</t>
+  </si>
+  <si>
+    <t>ZOOM HAPPY</t>
+  </si>
+  <si>
+    <t>AIR MAX TN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SB DUNK </t>
+  </si>
+  <si>
+    <t>JORDAN AURA</t>
+  </si>
+  <si>
+    <t>SHOX GUSANO</t>
+  </si>
+  <si>
+    <t>LE COQ SPORTIF</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
     <t>EU 40 AL 45</t>
   </si>
   <si>
-    <t>ADIZERO</t>
-  </si>
-  <si>
-    <t>EU 36 AL 44</t>
-  </si>
-  <si>
-    <t>M Y H</t>
+    <t>EU 40 AL 46</t>
+  </si>
+  <si>
+    <t>EU 40 AL 47</t>
+  </si>
+  <si>
+    <t>EU 40 AL 48</t>
+  </si>
+  <si>
+    <t>LACOSTE TABLA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AF1 </t>
+  </si>
+  <si>
+    <t>PUMA</t>
+  </si>
+  <si>
+    <t>PARK</t>
   </si>
   <si>
     <t>EU 36 AL 45</t>
   </si>
   <si>
-    <t>ASICS</t>
-  </si>
-  <si>
-    <t>ASICS RUN</t>
-  </si>
-  <si>
-    <t>NEW BALANCE</t>
-  </si>
-  <si>
-    <t>ARMANI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NEW BALANCE </t>
-  </si>
-  <si>
-    <t>COACH</t>
-  </si>
-  <si>
-    <t>SAMBA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REEBOK </t>
-  </si>
-  <si>
-    <t>LACOSTE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LACOSTE ALPACINO </t>
-  </si>
-  <si>
-    <t xml:space="preserve">VANS </t>
-  </si>
-  <si>
-    <t>ZOOM PEGASUS</t>
-  </si>
-  <si>
-    <t>SB PARRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LACOSTE </t>
-  </si>
-  <si>
-    <t>SB SUPREME</t>
-  </si>
-  <si>
-    <t>AF1 SUPREME</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NIKE </t>
-  </si>
-  <si>
-    <t>LOUIS VUITTON</t>
-  </si>
-  <si>
-    <t>SKATE</t>
-  </si>
-  <si>
-    <t>ZOOM HAPPY</t>
-  </si>
-  <si>
-    <t>JORDAN AURA</t>
-  </si>
-  <si>
-    <t>SHOX GUSANO</t>
-  </si>
-  <si>
-    <t>EU 40 AL 46</t>
-  </si>
-  <si>
-    <t>EU 40 AL 47</t>
-  </si>
-  <si>
-    <t>EU 40 AL 48</t>
-  </si>
-  <si>
-    <t>LACOSTE TABLA</t>
-  </si>
-  <si>
-    <t>PUMA</t>
-  </si>
-  <si>
     <t>SUPERMAGMA</t>
   </si>
   <si>
     <t>INITIATOR</t>
   </si>
   <si>
+    <t>JORDAN R1 LOW PARIS TOP</t>
+  </si>
+  <si>
     <t>JORDAN R3 TRAVIS SCOTT</t>
   </si>
   <si>
+    <t>JORDAN R3</t>
+  </si>
+  <si>
     <t>JORDAN CLUB</t>
   </si>
   <si>
+    <t>SUEDE XL</t>
+  </si>
+  <si>
     <t>EU 36 AL 43</t>
   </si>
   <si>
@@ -216,7 +296,7 @@
     <t xml:space="preserve">VANS  </t>
   </si>
   <si>
-    <t>JORDAN RETRO 1 LOW</t>
+    <t>VISION</t>
   </si>
   <si>
     <t>BROOKS</t>
@@ -225,76 +305,103 @@
     <t xml:space="preserve">HYPERION MAX </t>
   </si>
   <si>
+    <t>AIR MAX 97</t>
+  </si>
+  <si>
+    <t>AIR MAX 2000</t>
+  </si>
+  <si>
+    <t>AIR MAX CORRELATE</t>
+  </si>
+  <si>
+    <t>NOCTA</t>
+  </si>
+  <si>
+    <t>TEKNO</t>
+  </si>
+  <si>
     <t xml:space="preserve">ADIDAS </t>
   </si>
   <si>
     <t>SUPER STAR</t>
   </si>
   <si>
+    <t>V2K</t>
+  </si>
+  <si>
+    <t>SL-72</t>
+  </si>
+  <si>
+    <t>SHOX</t>
+  </si>
+  <si>
+    <t>CAMPUS</t>
+  </si>
+  <si>
+    <t>SB JARRITO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HYLANE </t>
+  </si>
+  <si>
+    <t>DIESEL</t>
+  </si>
+  <si>
+    <t>JORDAN RETRO 11</t>
+  </si>
+  <si>
+    <t>ANUEL</t>
+  </si>
+  <si>
+    <t>ON CLOUD</t>
+  </si>
+  <si>
+    <t>TN PLUS</t>
+  </si>
+  <si>
+    <t>ADIDAS TERREX</t>
+  </si>
+  <si>
+    <t>ADIDAS FASHION</t>
+  </si>
+  <si>
+    <t>ALTRA</t>
+  </si>
+  <si>
+    <t>JORDAN LOW PARIS PERLAS</t>
+  </si>
+  <si>
+    <t>EQUIPMENT</t>
+  </si>
+  <si>
+    <t>ADISTAR</t>
+  </si>
+  <si>
+    <t>EXCHANGE</t>
+  </si>
+  <si>
+    <t>TABLA</t>
+  </si>
+  <si>
+    <t>SAMBA XLG</t>
+  </si>
+  <si>
+    <t>CORTEZ</t>
+  </si>
+  <si>
+    <t>JORDAN RETRO 4</t>
+  </si>
+  <si>
+    <t>SHOX SUPREME</t>
+  </si>
+  <si>
+    <t>ERA</t>
+  </si>
+  <si>
     <t>NIKE V2K</t>
   </si>
   <si>
-    <t>CAMPUS</t>
-  </si>
-  <si>
-    <t>SB JARRITO</t>
-  </si>
-  <si>
-    <t>DIESEL</t>
-  </si>
-  <si>
-    <t>JORDAN RETRO 11</t>
-  </si>
-  <si>
-    <t>ON CLOUD</t>
-  </si>
-  <si>
-    <t>TN PLUS</t>
-  </si>
-  <si>
-    <t>ADIDAS TERREX</t>
-  </si>
-  <si>
-    <t>ADIDAS FASHION</t>
-  </si>
-  <si>
-    <t>ALTRA</t>
-  </si>
-  <si>
-    <t>EQUIPMENT</t>
-  </si>
-  <si>
-    <t>TRAIL</t>
-  </si>
-  <si>
-    <t>ADISTAR</t>
-  </si>
-  <si>
-    <t>EXCHANGE</t>
-  </si>
-  <si>
-    <t>TABLA</t>
-  </si>
-  <si>
-    <t>SAMBA XLG</t>
-  </si>
-  <si>
-    <t>CORTEZ</t>
-  </si>
-  <si>
-    <t>JORDAN RETRO 4</t>
-  </si>
-  <si>
-    <t>SHOX SUPREME</t>
-  </si>
-  <si>
-    <t>DISPONIBLE</t>
-  </si>
-  <si>
-    <t>S</t>
-  </si>
-  <si>
-    <t>P-6000</t>
+    <t>XL BMW</t>
   </si>
   <si>
     <t>X MOSTER</t>
@@ -318,119 +425,29 @@
     <t xml:space="preserve">SMAH </t>
   </si>
   <si>
-    <t xml:space="preserve">HYLANE </t>
-  </si>
-  <si>
-    <t>BOUNCE</t>
-  </si>
-  <si>
-    <t>SL-72</t>
-  </si>
-  <si>
-    <t>ASCIS RUN</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>LE COQ SPORTIF</t>
-  </si>
-  <si>
-    <t>RUN</t>
-  </si>
-  <si>
-    <t>SHOX</t>
-  </si>
-  <si>
-    <t>AF1</t>
-  </si>
-  <si>
-    <t>V2K</t>
-  </si>
-  <si>
-    <t>TEKNO</t>
-  </si>
-  <si>
-    <t>NOCTA</t>
-  </si>
-  <si>
-    <t>AIR MAX CORRELATE</t>
-  </si>
-  <si>
-    <t>AIR MAX 2000</t>
-  </si>
-  <si>
-    <t>AIR MAX 97</t>
-  </si>
-  <si>
-    <t>SB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AF1 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">SB DUNK </t>
-  </si>
-  <si>
-    <t>AIR MAX TN</t>
-  </si>
-  <si>
-    <t>P-6001</t>
-  </si>
-  <si>
-    <t>P-7000</t>
-  </si>
-  <si>
-    <t>P7000</t>
-  </si>
-  <si>
-    <t>PARK</t>
-  </si>
-  <si>
-    <t>XL BMW</t>
-  </si>
-  <si>
-    <t>SUEDE XL</t>
-  </si>
-  <si>
-    <t>ANUEL</t>
-  </si>
-  <si>
-    <t>CLUB</t>
-  </si>
-  <si>
-    <t>FLOATZIG</t>
-  </si>
-  <si>
-    <t>ERA</t>
-  </si>
-  <si>
-    <t>HYLANE</t>
-  </si>
-  <si>
-    <t>KNU</t>
-  </si>
-  <si>
-    <t>VISION</t>
-  </si>
-  <si>
-    <t>JORDAN RETRO 1</t>
-  </si>
-  <si>
-    <t>JORDAN R1 LOW PARIS TOP</t>
-  </si>
-  <si>
-    <t>JORDAN R3</t>
-  </si>
-  <si>
-    <t>JORDAN LOW PARIS PERLAS</t>
+    <t xml:space="preserve">M </t>
+  </si>
+  <si>
+    <t>TN DAMA</t>
+  </si>
+  <si>
+    <t>P6000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FREE METCON </t>
+  </si>
+  <si>
+    <t>QSTAR</t>
+  </si>
+  <si>
+    <t>MONSTER</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -453,7 +470,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -469,6 +486,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF6C3FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCCFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -500,7 +523,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -534,6 +557,21 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -557,7 +595,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -853,8 +891,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F75DB620-AF17-408B-81D4-431B9D551CF9}">
-  <dimension ref="B2:I189"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B2:I193"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4.42578125" customWidth="1"/>
     <col min="2" max="2" width="14.28515625" style="7" bestFit="1" customWidth="1"/>
@@ -866,7 +904,7 @@
     <col min="9" max="9" width="16" style="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:9">
       <c r="B2" s="4" t="s">
         <v>0</v>
       </c>
@@ -889,15 +927,15 @@
         <v>6</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9">
       <c r="B3" s="5">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" s="13" t="s">
         <v>9</v>
@@ -916,24 +954,24 @@
         <v>145000</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9">
       <c r="B4" s="5">
         <v>2</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G4" s="2">
         <v>95000</v>
@@ -943,24 +981,24 @@
         <v>140000</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9">
       <c r="B5" s="5">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D5" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G5" s="2">
         <v>90000</v>
@@ -970,24 +1008,24 @@
         <v>135000</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9">
       <c r="B6" s="5">
         <v>4</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D6" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G6" s="2">
         <v>70000</v>
@@ -997,24 +1035,24 @@
         <v>115000</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9">
       <c r="B7" s="5">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D7" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G7" s="2">
         <v>70000</v>
@@ -1024,24 +1062,24 @@
         <v>115000</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9">
       <c r="B8" s="5">
         <v>6</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D8" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G8" s="2">
         <v>70000</v>
@@ -1051,21 +1089,21 @@
         <v>115000</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9">
       <c r="B9" s="5">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D9" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>74</v>
+        <v>22</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>11</v>
@@ -1078,21 +1116,21 @@
         <v>135000</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9">
       <c r="B10" s="5">
         <v>8</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>11</v>
@@ -1105,24 +1143,24 @@
         <v>135000</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9">
       <c r="B11" s="5">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G11" s="2">
         <v>90000</v>
@@ -1132,24 +1170,24 @@
         <v>135000</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9">
       <c r="B12" s="5">
         <v>10</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G12" s="2">
         <v>85000</v>
@@ -1159,24 +1197,24 @@
         <v>130000</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9">
       <c r="B13" s="5">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G13" s="2">
         <v>85000</v>
@@ -1186,21 +1224,21 @@
         <v>130000</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9">
       <c r="B14" s="5">
         <v>12</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>11</v>
@@ -1213,21 +1251,21 @@
         <v>135000</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9">
       <c r="B15" s="5">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>112</v>
+        <v>29</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>11</v>
@@ -1240,21 +1278,21 @@
         <v>130000</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9">
       <c r="B16" s="5">
         <v>14</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D16" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>112</v>
+        <v>29</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>11</v>
@@ -1267,24 +1305,24 @@
         <v>130000</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9">
       <c r="B17" s="5">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D17" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F17" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="G17" s="2">
         <v>85000</v>
@@ -1294,21 +1332,21 @@
         <v>130000</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9">
       <c r="B18" s="5">
         <v>16</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>11</v>
@@ -1321,21 +1359,21 @@
         <v>125000</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9">
       <c r="B19" s="5">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>11</v>
@@ -1348,21 +1386,21 @@
         <v>125000</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9">
       <c r="B20" s="5">
         <v>18</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>11</v>
@@ -1375,21 +1413,21 @@
         <v>135000</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9">
       <c r="B21" s="5">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>95</v>
+        <v>32</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>11</v>
@@ -1402,21 +1440,21 @@
         <v>125000</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9">
       <c r="B22" s="5">
         <v>20</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>11</v>
@@ -1429,21 +1467,21 @@
         <v>125000</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9">
       <c r="B23" s="5">
         <v>21</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>98</v>
+        <v>34</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>11</v>
@@ -1456,21 +1494,21 @@
         <v>130000</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9">
       <c r="B24" s="5">
         <v>22</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>11</v>
@@ -1483,21 +1521,21 @@
         <v>125000</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9">
       <c r="B25" s="5">
         <v>23</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D25" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>11</v>
@@ -1510,24 +1548,24 @@
         <v>140000</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9">
       <c r="B26" s="5">
         <v>24</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G26" s="2">
         <v>100000</v>
@@ -1537,21 +1575,21 @@
         <v>145000</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9">
       <c r="B27" s="5">
         <v>25</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>118</v>
+        <v>39</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>11</v>
@@ -1564,21 +1602,21 @@
         <v>140000</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9">
       <c r="B28" s="5">
         <v>26</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>11</v>
@@ -1591,24 +1629,24 @@
         <v>140000</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" spans="2:9">
       <c r="B29" s="5">
         <v>27</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>121</v>
+        <v>43</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G29" s="2">
         <v>110000</v>
@@ -1618,24 +1656,24 @@
         <v>155000</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="2:9">
       <c r="B30" s="5">
         <v>28</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>122</v>
+        <v>44</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G30" s="2">
         <v>100000</v>
@@ -1645,21 +1683,21 @@
         <v>145000</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="2:9">
       <c r="B31" s="5">
         <v>29</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>119</v>
+        <v>45</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>11</v>
@@ -1672,24 +1710,24 @@
         <v>125000</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="32" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" spans="2:9">
       <c r="B32" s="5">
         <v>30</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E32" s="1">
         <v>740</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G32" s="2">
         <v>75000</v>
@@ -1699,21 +1737,21 @@
         <v>120000</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="33" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" spans="2:9">
       <c r="B33" s="5">
         <v>31</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>11</v>
@@ -1726,24 +1764,24 @@
         <v>125000</v>
       </c>
       <c r="I33" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="34" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="2:9">
       <c r="B34" s="5">
         <v>32</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D34" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G34" s="2">
         <v>95000</v>
@@ -1753,21 +1791,21 @@
         <v>140000</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="35" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35" spans="2:9">
       <c r="B35" s="5">
         <v>33</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D35" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>107</v>
+        <v>48</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>11</v>
@@ -1780,21 +1818,21 @@
         <v>140000</v>
       </c>
       <c r="I35" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="36" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="36" spans="2:9">
       <c r="B36" s="5">
         <v>34</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D36" s="13" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>11</v>
@@ -1807,24 +1845,24 @@
         <v>135000</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="37" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="37" spans="2:9">
       <c r="B37" s="5">
         <v>35</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D37" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G37" s="2">
         <v>95000</v>
@@ -1834,24 +1872,24 @@
         <v>140000</v>
       </c>
       <c r="I37" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="38" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38" spans="2:9">
       <c r="B38" s="5">
         <v>36</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D38" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>107</v>
+        <v>48</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G38" s="2">
         <v>95000</v>
@@ -1861,21 +1899,21 @@
         <v>140000</v>
       </c>
       <c r="I38" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="39" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="39" spans="2:9">
       <c r="B39" s="5">
         <v>37</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D39" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>11</v>
@@ -1888,21 +1926,21 @@
         <v>140000</v>
       </c>
       <c r="I39" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="40" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="40" spans="2:9">
       <c r="B40" s="5">
         <v>38</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D40" s="13" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>11</v>
@@ -1915,24 +1953,24 @@
         <v>140000</v>
       </c>
       <c r="I40" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="41" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="41" spans="2:9">
       <c r="B41" s="5">
         <v>39</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D41" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>124</v>
+        <v>54</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G41" s="2">
         <v>90000</v>
@@ -1942,24 +1980,24 @@
         <v>135000</v>
       </c>
       <c r="I41" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="42" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="42" spans="2:9">
       <c r="B42" s="5">
         <v>40</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D42" s="13" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G42" s="2">
         <v>90000</v>
@@ -1969,24 +2007,24 @@
         <v>135000</v>
       </c>
       <c r="I42" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="43" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="43" spans="2:9">
       <c r="B43" s="5">
         <v>41</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D43" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>84</v>
+        <v>57</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G43" s="2">
         <v>100000</v>
@@ -1996,24 +2034,24 @@
         <v>145000</v>
       </c>
       <c r="I43" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="44" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44" spans="2:9">
       <c r="B44" s="5">
         <v>42</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D44" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>111</v>
+        <v>58</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G44" s="2">
         <v>100000</v>
@@ -2023,24 +2061,24 @@
         <v>145000</v>
       </c>
       <c r="I44" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="45" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="45" spans="2:9">
       <c r="B45" s="5">
         <v>43</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D45" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G45" s="2">
         <v>90000</v>
@@ -2050,21 +2088,21 @@
         <v>135000</v>
       </c>
       <c r="I45" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="46" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="46" spans="2:9">
       <c r="B46" s="5">
         <v>44</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D46" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>11</v>
@@ -2077,21 +2115,21 @@
         <v>130000</v>
       </c>
       <c r="I46" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="47" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="47" spans="2:9">
       <c r="B47" s="5">
         <v>45</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D47" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>109</v>
+        <v>61</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>11</v>
@@ -2104,21 +2142,21 @@
         <v>140000</v>
       </c>
       <c r="I47" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="48" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="48" spans="2:9">
       <c r="B48" s="5">
         <v>46</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D48" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>109</v>
+        <v>61</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>11</v>
@@ -2131,24 +2169,24 @@
         <v>140000</v>
       </c>
       <c r="I48" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="49" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="49" spans="2:9">
       <c r="B49" s="5">
         <v>47</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D49" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>109</v>
+        <v>61</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G49" s="2">
         <v>100000</v>
@@ -2158,21 +2196,21 @@
         <v>145000</v>
       </c>
       <c r="I49" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="50" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="50" spans="2:9">
       <c r="B50" s="5">
         <v>48</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D50" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>11</v>
@@ -2185,21 +2223,21 @@
         <v>155000</v>
       </c>
       <c r="I50" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="51" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="51" spans="2:9">
       <c r="B51" s="5">
         <v>49</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D51" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>11</v>
@@ -2212,24 +2250,24 @@
         <v>155000</v>
       </c>
       <c r="I51" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="52" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="52" spans="2:9">
       <c r="B52" s="5">
         <v>50</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D52" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G52" s="2">
         <v>100000</v>
@@ -2239,21 +2277,21 @@
         <v>145000</v>
       </c>
       <c r="I52" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="53" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="53" spans="2:9">
       <c r="B53" s="5">
         <v>51</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D53" s="13" t="s">
-        <v>97</v>
+        <v>64</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>97</v>
+        <v>64</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>11</v>
@@ -2266,24 +2304,24 @@
         <v>135000</v>
       </c>
       <c r="I53" s="5" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="54" spans="2:9" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="54" spans="2:9">
       <c r="B54" s="5">
         <v>52</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D54" s="13" t="s">
-        <v>97</v>
+        <v>64</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>97</v>
+        <v>64</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>19</v>
+        <v>66</v>
       </c>
       <c r="G54" s="2">
         <v>95000</v>
@@ -2293,24 +2331,24 @@
         <v>140000</v>
       </c>
       <c r="I54" s="5" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="55" spans="2:9" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="55" spans="2:9">
       <c r="B55" s="5">
         <v>53</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D55" s="13" t="s">
-        <v>97</v>
+        <v>64</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>97</v>
+        <v>64</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="G55" s="2">
         <v>95000</v>
@@ -2320,24 +2358,24 @@
         <v>140000</v>
       </c>
       <c r="I55" s="5" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="56" spans="2:9" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="56" spans="2:9">
       <c r="B56" s="5">
         <v>54</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D56" s="13" t="s">
-        <v>97</v>
+        <v>64</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>97</v>
+        <v>64</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="G56" s="2">
         <v>95000</v>
@@ -2347,24 +2385,24 @@
         <v>140000</v>
       </c>
       <c r="I56" s="5" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="57" spans="2:9" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="57" spans="2:9">
       <c r="B57" s="5">
         <v>55</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D57" s="13" t="s">
-        <v>97</v>
+        <v>64</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>97</v>
+        <v>64</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="G57" s="2">
         <v>95000</v>
@@ -2374,21 +2412,21 @@
         <v>140000</v>
       </c>
       <c r="I57" s="5" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="58" spans="2:9" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="58" spans="2:9">
       <c r="B58" s="5">
         <v>56</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D58" s="13" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>11</v>
@@ -2401,21 +2439,21 @@
         <v>145000</v>
       </c>
       <c r="I58" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="59" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="59" spans="2:9">
       <c r="B59" s="5">
         <v>57</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D59" s="13" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>108</v>
+        <v>71</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>11</v>
@@ -2428,24 +2466,24 @@
         <v>120000</v>
       </c>
       <c r="I59" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="60" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="60" spans="2:9">
       <c r="B60" s="5">
         <v>58</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D60" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>74</v>
+        <v>22</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G60" s="2">
         <v>85000</v>
@@ -2455,24 +2493,24 @@
         <v>130000</v>
       </c>
       <c r="I60" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="61" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="61" spans="2:9">
       <c r="B61" s="5">
         <v>59</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D61" s="13" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>114</v>
+        <v>73</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G61" s="2">
         <v>95000</v>
@@ -2482,24 +2520,24 @@
         <v>140000</v>
       </c>
       <c r="I61" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="62" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="62" spans="2:9">
       <c r="B62" s="5">
         <v>60</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D62" s="13" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>114</v>
+        <v>73</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G62" s="2">
         <v>95000</v>
@@ -2509,24 +2547,24 @@
         <v>140000</v>
       </c>
       <c r="I62" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="63" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="63" spans="2:9">
       <c r="B63" s="5">
         <v>61</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D63" s="13" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>114</v>
+        <v>73</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>23</v>
+        <v>74</v>
       </c>
       <c r="G63" s="2">
         <v>95000</v>
@@ -2536,15 +2574,15 @@
         <v>140000</v>
       </c>
       <c r="I63" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="64" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="64" spans="2:9">
       <c r="B64" s="5">
         <v>62</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D64" s="13" t="s">
         <v>9</v>
@@ -2563,15 +2601,15 @@
         <v>140000</v>
       </c>
       <c r="I64" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="65" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="65" spans="2:9">
       <c r="B65" s="5">
         <v>63</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D65" s="13" t="s">
         <v>9</v>
@@ -2590,15 +2628,15 @@
         <v>140000</v>
       </c>
       <c r="I65" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="66" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="66" spans="2:9">
       <c r="B66" s="5">
         <v>64</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D66" s="13" t="s">
         <v>9</v>
@@ -2617,15 +2655,15 @@
         <v>140000</v>
       </c>
       <c r="I66" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="67" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="67" spans="2:9">
       <c r="B67" s="5">
         <v>65</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D67" s="13" t="s">
         <v>9</v>
@@ -2644,24 +2682,24 @@
         <v>140000</v>
       </c>
       <c r="I67" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="68" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="68" spans="2:9">
       <c r="B68" s="5">
         <v>66</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D68" s="13" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G68" s="2">
         <v>110000</v>
@@ -2671,24 +2709,24 @@
         <v>155000</v>
       </c>
       <c r="I68" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="69" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="69" spans="2:9">
       <c r="B69" s="5">
         <v>67</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D69" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G69" s="2">
         <v>100000</v>
@@ -2698,24 +2736,24 @@
         <v>145000</v>
       </c>
       <c r="I69" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="70" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="70" spans="2:9">
       <c r="B70" s="5">
         <v>68</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D70" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G70" s="2">
         <v>100000</v>
@@ -2725,24 +2763,24 @@
         <v>145000</v>
       </c>
       <c r="I70" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="71" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="71" spans="2:9">
       <c r="B71" s="5">
         <v>69</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D71" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G71" s="2">
         <v>100000</v>
@@ -2752,24 +2790,24 @@
         <v>145000</v>
       </c>
       <c r="I71" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="72" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="72" spans="2:9">
       <c r="B72" s="5">
         <v>70</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D72" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>126</v>
+        <v>79</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G72" s="2">
         <v>110000</v>
@@ -2779,24 +2817,24 @@
         <v>155000</v>
       </c>
       <c r="I72" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="73" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="73" spans="2:9">
       <c r="B73" s="5">
         <v>71</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D73" s="13" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G73" s="2">
         <v>95000</v>
@@ -2806,24 +2844,24 @@
         <v>140000</v>
       </c>
       <c r="I73" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="74" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="74" spans="2:9">
       <c r="B74" s="5">
         <v>72</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D74" s="13" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G74" s="2">
         <v>75000</v>
@@ -2833,24 +2871,24 @@
         <v>120000</v>
       </c>
       <c r="I74" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="75" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="75" spans="2:9">
       <c r="B75" s="5">
         <v>73</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D75" s="13" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G75" s="2">
         <v>95000</v>
@@ -2860,24 +2898,24 @@
         <v>140000</v>
       </c>
       <c r="I75" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="76" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="76" spans="2:9">
       <c r="B76" s="5">
         <v>74</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D76" s="13" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>114</v>
+        <v>73</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G76" s="2">
         <v>100000</v>
@@ -2887,24 +2925,24 @@
         <v>145000</v>
       </c>
       <c r="I76" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="77" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="77" spans="2:9">
       <c r="B77" s="5">
         <v>75</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D77" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>107</v>
+        <v>48</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G77" s="2">
         <v>110000</v>
@@ -2914,24 +2952,24 @@
         <v>155000</v>
       </c>
       <c r="I77" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="78" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="78" spans="2:9">
       <c r="B78" s="5">
         <v>76</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D78" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>107</v>
+        <v>48</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G78" s="2">
         <v>110000</v>
@@ -2941,24 +2979,24 @@
         <v>155000</v>
       </c>
       <c r="I78" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="79" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="79" spans="2:9">
       <c r="B79" s="5">
         <v>77</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D79" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>107</v>
+        <v>48</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G79" s="2">
         <v>110000</v>
@@ -2968,24 +3006,24 @@
         <v>155000</v>
       </c>
       <c r="I79" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="80" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="80" spans="2:9">
       <c r="B80" s="5">
         <v>78</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D80" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>107</v>
+        <v>48</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>55</v>
+        <v>82</v>
       </c>
       <c r="G80" s="2">
         <v>90000</v>
@@ -2995,24 +3033,24 @@
         <v>135000</v>
       </c>
       <c r="I80" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="81" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="81" spans="2:9">
       <c r="B81" s="5">
         <v>79</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D81" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>107</v>
+        <v>48</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G81" s="2">
         <v>90000</v>
@@ -3022,24 +3060,24 @@
         <v>135000</v>
       </c>
       <c r="I81" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="82" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="82" spans="2:9">
       <c r="B82" s="5">
         <v>80</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D82" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>107</v>
+        <v>48</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G82" s="2">
         <v>90000</v>
@@ -3049,24 +3087,24 @@
         <v>135000</v>
       </c>
       <c r="I82" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="83" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="83" spans="2:9">
       <c r="B83" s="5">
         <v>81</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D83" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>107</v>
+        <v>48</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G83" s="2">
         <v>90000</v>
@@ -3076,24 +3114,24 @@
         <v>135000</v>
       </c>
       <c r="I83" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="84" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="84" spans="2:9">
       <c r="B84" s="5">
         <v>82</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D84" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>107</v>
+        <v>48</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G84" s="2">
         <v>90000</v>
@@ -3103,21 +3141,21 @@
         <v>135000</v>
       </c>
       <c r="I84" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="85" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="85" spans="2:9">
       <c r="B85" s="5">
         <v>83</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D85" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>107</v>
+        <v>48</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>11</v>
@@ -3130,21 +3168,21 @@
         <v>135000</v>
       </c>
       <c r="I85" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="86" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="86" spans="2:9">
       <c r="B86" s="5">
         <v>84</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D86" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="E86" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="E86" s="1" t="s">
-        <v>42</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>11</v>
@@ -3157,21 +3195,21 @@
         <v>150000</v>
       </c>
       <c r="I86" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="87" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="87" spans="2:9">
       <c r="B87" s="5">
         <v>85</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D87" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="E87" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="E87" s="1" t="s">
-        <v>42</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>11</v>
@@ -3184,21 +3222,21 @@
         <v>150000</v>
       </c>
       <c r="I87" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="88" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="88" spans="2:9">
       <c r="B88" s="5">
         <v>86</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D88" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="E88" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="E88" s="1" t="s">
-        <v>42</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>11</v>
@@ -3211,21 +3249,21 @@
         <v>150000</v>
       </c>
       <c r="I88" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="89" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="89" spans="2:9">
       <c r="B89" s="5">
         <v>87</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D89" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="E89" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="E89" s="1" t="s">
-        <v>42</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>11</v>
@@ -3238,21 +3276,21 @@
         <v>150000</v>
       </c>
       <c r="I89" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="90" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="90" spans="2:9">
       <c r="B90" s="5">
         <v>88</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D90" s="13" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>57</v>
+        <v>84</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>11</v>
@@ -3265,24 +3303,24 @@
         <v>150000</v>
       </c>
       <c r="I90" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="91" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="91" spans="2:9">
       <c r="B91" s="5">
         <v>89</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D91" s="13" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>123</v>
+        <v>85</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G91" s="2">
         <v>105000</v>
@@ -3292,24 +3330,24 @@
         <v>150000</v>
       </c>
       <c r="I91" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="92" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="92" spans="2:9">
       <c r="B92" s="5">
         <v>90</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D92" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G92" s="2">
         <v>105000</v>
@@ -3319,21 +3357,21 @@
         <v>150000</v>
       </c>
       <c r="I92" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="93" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="93" spans="2:9">
       <c r="B93" s="5">
         <v>91</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D93" s="13" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>60</v>
+        <v>87</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>11</v>
@@ -3346,21 +3384,21 @@
         <v>160000</v>
       </c>
       <c r="I93" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="94" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="94" spans="2:9">
       <c r="B94" s="5">
         <v>92</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D94" s="13" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>60</v>
+        <v>87</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>11</v>
@@ -3373,21 +3411,21 @@
         <v>160000</v>
       </c>
       <c r="I94" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="95" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="95" spans="2:9">
       <c r="B95" s="5">
         <v>93</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D95" s="13" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>60</v>
+        <v>87</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>11</v>
@@ -3400,21 +3438,21 @@
         <v>160000</v>
       </c>
       <c r="I95" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="96" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="96" spans="2:9">
       <c r="B96" s="5">
         <v>94</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D96" s="13" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>60</v>
+        <v>87</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>11</v>
@@ -3427,24 +3465,24 @@
         <v>160000</v>
       </c>
       <c r="I96" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="97" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="97" spans="2:9">
       <c r="B97" s="5">
         <v>95</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D97" s="13" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>60</v>
+        <v>87</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>19</v>
+        <v>66</v>
       </c>
       <c r="G97" s="2">
         <v>115000</v>
@@ -3454,24 +3492,24 @@
         <v>160000</v>
       </c>
       <c r="I97" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="98" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="98" spans="2:9">
       <c r="B98" s="5">
         <v>96</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D98" s="13" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G98" s="2">
         <v>95000</v>
@@ -3481,21 +3519,21 @@
         <v>140000</v>
       </c>
       <c r="I98" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="99" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="99" spans="2:9">
       <c r="B99" s="5">
         <v>97</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D99" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>11</v>
@@ -3508,21 +3546,21 @@
         <v>140000</v>
       </c>
       <c r="I99" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="100" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="100" spans="2:9">
       <c r="B100" s="5">
         <v>98</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D100" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>11</v>
@@ -3535,21 +3573,21 @@
         <v>150000</v>
       </c>
       <c r="I100" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="101" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="101" spans="2:9">
       <c r="B101" s="5">
         <v>99</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D101" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>11</v>
@@ -3562,24 +3600,24 @@
         <v>140000</v>
       </c>
       <c r="I101" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="102" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="102" spans="2:9">
       <c r="B102" s="5">
         <v>100</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D102" s="13" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G102" s="2">
         <v>100000</v>
@@ -3589,24 +3627,24 @@
         <v>145000</v>
       </c>
       <c r="I102" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="103" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="103" spans="2:9">
       <c r="B103" s="5">
         <v>101</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D103" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G103" s="2">
         <v>100000</v>
@@ -3616,24 +3654,24 @@
         <v>145000</v>
       </c>
       <c r="I103" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="104" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="104" spans="2:9">
       <c r="B104" s="5">
         <v>102</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D104" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G104" s="2">
         <v>100000</v>
@@ -3643,24 +3681,24 @@
         <v>145000</v>
       </c>
       <c r="I104" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="105" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="105" spans="2:9">
       <c r="B105" s="5">
         <v>103</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D105" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G105" s="2">
         <v>100000</v>
@@ -3670,21 +3708,21 @@
         <v>145000</v>
       </c>
       <c r="I105" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="106" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="106" spans="2:9">
       <c r="B106" s="5">
         <v>104</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D106" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>11</v>
@@ -3697,24 +3735,24 @@
         <v>165000</v>
       </c>
       <c r="I106" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="107" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="107" spans="2:9">
       <c r="B107" s="5">
         <v>105</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D107" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G107" s="2">
         <v>90000</v>
@@ -3724,21 +3762,21 @@
         <v>135000</v>
       </c>
       <c r="I107" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="108" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="108" spans="2:9">
       <c r="B108" s="5">
         <v>106</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D108" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>11</v>
@@ -3751,24 +3789,24 @@
         <v>125000</v>
       </c>
       <c r="I108" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="109" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="109" spans="2:9">
       <c r="B109" s="5">
         <v>107</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D109" s="13" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G109" s="2">
         <v>85000</v>
@@ -3778,24 +3816,24 @@
         <v>130000</v>
       </c>
       <c r="I109" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="110" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="110" spans="2:9">
       <c r="B110" s="5">
         <v>108</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D110" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G110" s="2">
         <v>105000</v>
@@ -3805,21 +3843,21 @@
         <v>150000</v>
       </c>
       <c r="I110" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="111" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="111" spans="2:9">
       <c r="B111" s="5">
         <v>109</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D111" s="13" t="s">
-        <v>97</v>
+        <v>64</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>97</v>
+        <v>64</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>11</v>
@@ -3832,24 +3870,24 @@
         <v>145000</v>
       </c>
       <c r="I111" s="5" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="112" spans="2:9" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="112" spans="2:9">
       <c r="B112" s="5">
         <v>110</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D112" s="13" t="s">
-        <v>97</v>
+        <v>64</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>97</v>
+        <v>64</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G112" s="2">
         <v>90000</v>
@@ -3859,24 +3897,24 @@
         <v>135000</v>
       </c>
       <c r="I112" s="5" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="113" spans="2:9" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="113" spans="2:9">
       <c r="B113" s="5">
         <v>111</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D113" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G113" s="2">
         <v>75000</v>
@@ -3886,24 +3924,24 @@
         <v>120000</v>
       </c>
       <c r="I113" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="114" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="114" spans="2:9">
       <c r="B114" s="5">
         <v>112</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D114" s="13" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G114" s="2">
         <v>85000</v>
@@ -3913,21 +3951,21 @@
         <v>130000</v>
       </c>
       <c r="I114" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="115" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="115" spans="2:9">
       <c r="B115" s="5">
         <v>113</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D115" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>11</v>
@@ -3940,21 +3978,21 @@
         <v>150000</v>
       </c>
       <c r="I115" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="116" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="116" spans="2:9">
       <c r="B116" s="5">
         <v>114</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D116" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>84</v>
+        <v>57</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>11</v>
@@ -3967,24 +4005,24 @@
         <v>145000</v>
       </c>
       <c r="I116" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="117" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="117" spans="2:9">
       <c r="B117" s="5">
         <v>115</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D117" s="13" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>121</v>
+        <v>43</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G117" s="2">
         <v>95000</v>
@@ -3994,24 +4032,24 @@
         <v>140000</v>
       </c>
       <c r="I117" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="118" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="118" spans="2:9">
       <c r="B118" s="5">
         <v>116</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D118" s="13" t="s">
-        <v>64</v>
+        <v>98</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>64</v>
+        <v>98</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G118" s="2">
         <v>100000</v>
@@ -4021,24 +4059,24 @@
         <v>145000</v>
       </c>
       <c r="I118" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="119" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="119" spans="2:9">
       <c r="B119" s="5">
         <v>117</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D119" s="13" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G119" s="2">
         <v>110000</v>
@@ -4048,24 +4086,24 @@
         <v>155000</v>
       </c>
       <c r="I119" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="120" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="120" spans="2:9">
       <c r="B120" s="5">
         <v>118</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D120" s="13" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E120" s="1">
         <v>9060</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G120" s="2">
         <v>110000</v>
@@ -4075,21 +4113,21 @@
         <v>155000</v>
       </c>
       <c r="I120" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="121" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="121" spans="2:9">
       <c r="B121" s="5">
         <v>119</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D121" s="13" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>11</v>
@@ -4102,24 +4140,24 @@
         <v>145000</v>
       </c>
       <c r="I121" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="122" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="122" spans="2:9">
       <c r="B122" s="5">
         <v>120</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D122" s="13" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G122" s="2">
         <v>95000</v>
@@ -4129,21 +4167,21 @@
         <v>140000</v>
       </c>
       <c r="I122" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="123" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="123" spans="2:9">
       <c r="B123" s="5">
         <v>121</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D123" s="13" t="s">
-        <v>66</v>
+        <v>101</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>66</v>
+        <v>101</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>11</v>
@@ -4156,21 +4194,21 @@
         <v>140000</v>
       </c>
       <c r="I123" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="124" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="124" spans="2:9">
       <c r="B124" s="5">
         <v>122</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D124" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>67</v>
+        <v>102</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>11</v>
@@ -4183,21 +4221,21 @@
         <v>145000</v>
       </c>
       <c r="I124" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="125" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="125" spans="2:9">
       <c r="B125" s="5">
         <v>123</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D125" s="13" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>11</v>
@@ -4210,24 +4248,24 @@
         <v>140000</v>
       </c>
       <c r="I125" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="126" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="126" spans="2:9">
       <c r="B126" s="5">
         <v>124</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D126" s="13" t="s">
-        <v>68</v>
+        <v>104</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>68</v>
+        <v>104</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G126" s="2">
         <v>90000</v>
@@ -4237,21 +4275,21 @@
         <v>135000</v>
       </c>
       <c r="I126" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="127" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="127" spans="2:9">
       <c r="B127" s="5">
         <v>125</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D127" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>69</v>
+        <v>105</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>11</v>
@@ -4264,24 +4302,24 @@
         <v>150000</v>
       </c>
       <c r="I127" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="128" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="128" spans="2:9">
       <c r="B128" s="6">
         <v>126</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D128" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E128" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F128" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="E128" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F128" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="G128" s="2">
         <v>85000</v>
@@ -4291,24 +4329,24 @@
         <v>130000</v>
       </c>
       <c r="I128" s="6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="129" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="129" spans="2:9">
       <c r="B129" s="6">
         <v>127</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D129" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F129" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="E129" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F129" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="G129" s="2">
         <v>85000</v>
@@ -4318,21 +4356,21 @@
         <v>130000</v>
       </c>
       <c r="I129" s="6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="130" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="130" spans="2:9">
       <c r="B130" s="6">
         <v>128</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D130" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>11</v>
@@ -4345,21 +4383,21 @@
         <v>135000</v>
       </c>
       <c r="I130" s="6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="131" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="131" spans="2:9">
       <c r="B131" s="6">
         <v>129</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D131" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>11</v>
@@ -4372,21 +4410,21 @@
         <v>135000</v>
       </c>
       <c r="I131" s="6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="132" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="132" spans="2:9">
       <c r="B132" s="6">
         <v>130</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D132" s="13" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>70</v>
+        <v>106</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>11</v>
@@ -4395,25 +4433,25 @@
         <v>105000</v>
       </c>
       <c r="H132" s="2">
-        <f t="shared" ref="H132:H179" si="2">G132+45000</f>
+        <f t="shared" ref="H132:H178" si="2">G132+45000</f>
         <v>150000</v>
       </c>
       <c r="I132" s="6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="133" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="133" spans="2:9">
       <c r="B133" s="6">
         <v>131</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D133" s="13" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>70</v>
+        <v>106</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>11</v>
@@ -4426,21 +4464,21 @@
         <v>150000</v>
       </c>
       <c r="I133" s="6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="134" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="134" spans="2:9">
       <c r="B134" s="6">
         <v>132</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D134" s="13" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>71</v>
+        <v>107</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>11</v>
@@ -4453,21 +4491,21 @@
         <v>145000</v>
       </c>
       <c r="I134" s="6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="135" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="135" spans="2:9">
       <c r="B135" s="6">
         <v>133</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D135" s="13" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>71</v>
+        <v>107</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>11</v>
@@ -4480,21 +4518,21 @@
         <v>145000</v>
       </c>
       <c r="I135" s="6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="136" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="136" spans="2:9">
       <c r="B136" s="6">
         <v>134</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D136" s="13" t="s">
-        <v>72</v>
+        <v>108</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>74</v>
+        <v>22</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>11</v>
@@ -4507,21 +4545,21 @@
         <v>160000</v>
       </c>
       <c r="I136" s="6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="137" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="137" spans="2:9">
       <c r="B137" s="6">
         <v>135</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D137" s="13" t="s">
-        <v>72</v>
+        <v>108</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>74</v>
+        <v>22</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>11</v>
@@ -4534,21 +4572,21 @@
         <v>160000</v>
       </c>
       <c r="I137" s="6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="138" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="138" spans="2:9">
       <c r="B138" s="6">
         <v>136</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D138" s="13" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>11</v>
@@ -4561,24 +4599,24 @@
         <v>145000</v>
       </c>
       <c r="I138" s="6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="139" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="139" spans="2:9">
       <c r="B139" s="6">
         <v>137</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D139" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G139" s="2">
         <v>105000</v>
@@ -4588,24 +4626,24 @@
         <v>150000</v>
       </c>
       <c r="I139" s="6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="140" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="140" spans="2:9">
       <c r="B140" s="6">
         <v>138</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D140" s="13" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G140" s="2">
         <v>110000</v>
@@ -4615,24 +4653,24 @@
         <v>155000</v>
       </c>
       <c r="I140" s="6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="141" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="141" spans="2:9">
       <c r="B141" s="6">
         <v>139</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D141" s="13" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G141" s="2">
         <v>110000</v>
@@ -4642,24 +4680,24 @@
         <v>155000</v>
       </c>
       <c r="I141" s="6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="142" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="142" spans="2:9">
       <c r="B142" s="6">
         <v>140</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D142" s="13" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G142" s="2">
         <v>110000</v>
@@ -4669,24 +4707,24 @@
         <v>155000</v>
       </c>
       <c r="I142" s="6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="143" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="143" spans="2:9">
       <c r="B143" s="6">
         <v>141</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D143" s="13" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G143" s="2">
         <v>110000</v>
@@ -4696,21 +4734,21 @@
         <v>155000</v>
       </c>
       <c r="I143" s="6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="144" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="144" spans="2:9">
       <c r="B144" s="6">
         <v>142</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D144" s="13" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>73</v>
+        <v>110</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>11</v>
@@ -4723,21 +4761,21 @@
         <v>135000</v>
       </c>
       <c r="I144" s="6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="145" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="145" spans="2:9">
       <c r="B145" s="6">
         <v>143</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D145" s="13" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>73</v>
+        <v>110</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>11</v>
@@ -4750,24 +4788,24 @@
         <v>135000</v>
       </c>
       <c r="I145" s="6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="146" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="146" spans="2:9">
       <c r="B146" s="6">
         <v>144</v>
       </c>
       <c r="C146" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D146" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="E146" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D146" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E146" s="1" t="s">
-        <v>74</v>
-      </c>
       <c r="F146" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G146" s="2">
         <v>85000</v>
@@ -4777,21 +4815,21 @@
         <v>130000</v>
       </c>
       <c r="I146" s="6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="147" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="147" spans="2:9">
       <c r="B147" s="6">
         <v>145</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D147" s="13" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>11</v>
@@ -4804,21 +4842,21 @@
         <v>130000</v>
       </c>
       <c r="I147" s="6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="148" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="148" spans="2:9">
       <c r="B148" s="6">
         <v>146</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D148" s="13" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>11</v>
@@ -4831,21 +4869,21 @@
         <v>130000</v>
       </c>
       <c r="I148" s="6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="149" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="149" spans="2:9">
       <c r="B149" s="6">
         <v>147</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D149" s="13" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>76</v>
+        <v>112</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>11</v>
@@ -4858,21 +4896,21 @@
         <v>125000</v>
       </c>
       <c r="I149" s="6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="150" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="150" spans="2:9">
       <c r="B150" s="6">
         <v>148</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D150" s="13" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>76</v>
+        <v>112</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>11</v>
@@ -4885,24 +4923,24 @@
         <v>125000</v>
       </c>
       <c r="I150" s="6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="151" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="151" spans="2:9">
       <c r="B151" s="6">
         <v>149</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D151" s="13" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G151" s="2">
         <v>110000</v>
@@ -4912,24 +4950,24 @@
         <v>155000</v>
       </c>
       <c r="I151" s="6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="152" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="152" spans="2:9">
       <c r="B152" s="6">
         <v>150</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D152" s="13" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G152" s="2">
         <v>95000</v>
@@ -4939,24 +4977,24 @@
         <v>140000</v>
       </c>
       <c r="I152" s="6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="153" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="153" spans="2:9">
       <c r="B153" s="6">
         <v>151</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D153" s="13" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G153" s="2">
         <v>105000</v>
@@ -4966,24 +5004,24 @@
         <v>150000</v>
       </c>
       <c r="I153" s="6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="154" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="154" spans="2:9">
       <c r="B154" s="6">
         <v>152</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D154" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G154" s="2">
         <v>90000</v>
@@ -4993,21 +5031,21 @@
         <v>135000</v>
       </c>
       <c r="I154" s="6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="155" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="155" spans="2:9">
       <c r="B155" s="6">
         <v>153</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D155" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>11</v>
@@ -5020,21 +5058,21 @@
         <v>140000</v>
       </c>
       <c r="I155" s="6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="156" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="156" spans="2:9">
       <c r="B156" s="6">
         <v>154</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D156" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>11</v>
@@ -5047,21 +5085,21 @@
         <v>150000</v>
       </c>
       <c r="I156" s="6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="157" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="157" spans="2:9">
       <c r="B157" s="6">
         <v>155</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D157" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>11</v>
@@ -5074,21 +5112,21 @@
         <v>150000</v>
       </c>
       <c r="I157" s="6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="158" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="158" spans="2:9">
       <c r="B158" s="6">
         <v>156</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D158" s="13" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>11</v>
@@ -5101,24 +5139,24 @@
         <v>130000</v>
       </c>
       <c r="I158" s="6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="159" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="159" spans="2:9">
       <c r="B159" s="8">
         <v>157</v>
       </c>
       <c r="C159" s="8" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D159" s="14" t="s">
         <v>9</v>
       </c>
       <c r="E159" s="9" t="s">
-        <v>63</v>
+        <v>119</v>
       </c>
       <c r="F159" s="9" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G159" s="10">
         <v>100000</v>
@@ -5128,24 +5166,24 @@
         <v>145000</v>
       </c>
       <c r="I159" s="8" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="160" spans="2:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="160" spans="2:9">
       <c r="B160" s="6">
         <v>158</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D160" s="13" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G160" s="2">
         <v>100000</v>
@@ -5156,18 +5194,18 @@
       </c>
       <c r="I160" s="6"/>
     </row>
-    <row r="161" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="161" spans="2:9">
       <c r="B161" s="6">
         <v>159</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D161" s="13" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>11</v>
@@ -5181,21 +5219,21 @@
       </c>
       <c r="I161" s="6"/>
     </row>
-    <row r="162" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="162" spans="2:9">
       <c r="B162" s="6">
         <v>160</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D162" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>84</v>
+        <v>57</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G162" s="2">
         <v>85000</v>
@@ -5206,18 +5244,18 @@
       </c>
       <c r="I162" s="6"/>
     </row>
-    <row r="163" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="163" spans="2:9">
       <c r="B163" s="6">
         <v>161</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D163" s="13" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>11</v>
@@ -5231,21 +5269,21 @@
       </c>
       <c r="I163" s="6"/>
     </row>
-    <row r="164" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="164" spans="2:9">
       <c r="B164" s="6">
         <v>162</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D164" s="13" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>85</v>
+        <v>121</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G164" s="2">
         <v>100000</v>
@@ -5256,18 +5294,18 @@
       </c>
       <c r="I164" s="6"/>
     </row>
-    <row r="165" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="165" spans="2:9">
       <c r="B165" s="6">
         <v>163</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D165" s="13" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>86</v>
+        <v>122</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>11</v>
@@ -5281,18 +5319,18 @@
       </c>
       <c r="I165" s="6"/>
     </row>
-    <row r="166" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="166" spans="2:9">
       <c r="B166" s="6">
         <v>164</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D166" s="13" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>87</v>
+        <v>123</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>11</v>
@@ -5306,18 +5344,18 @@
       </c>
       <c r="I166" s="6"/>
     </row>
-    <row r="167" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="167" spans="2:9">
       <c r="B167" s="6">
         <v>165</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D167" s="13" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>88</v>
+        <v>124</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>11</v>
@@ -5331,18 +5369,18 @@
       </c>
       <c r="I167" s="6"/>
     </row>
-    <row r="168" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="168" spans="2:9">
       <c r="B168" s="6">
         <v>166</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D168" s="13" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>88</v>
+        <v>124</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>11</v>
@@ -5356,18 +5394,18 @@
       </c>
       <c r="I168" s="6"/>
     </row>
-    <row r="169" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="169" spans="2:9">
       <c r="B169" s="6">
         <v>167</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D169" s="13" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>88</v>
+        <v>124</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>11</v>
@@ -5381,18 +5419,18 @@
       </c>
       <c r="I169" s="6"/>
     </row>
-    <row r="170" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="170" spans="2:9">
       <c r="B170" s="6">
         <v>168</v>
       </c>
       <c r="C170" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D170" s="13" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>88</v>
+        <v>124</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>11</v>
@@ -5406,18 +5444,18 @@
       </c>
       <c r="I170" s="6"/>
     </row>
-    <row r="171" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="171" spans="2:9">
       <c r="B171" s="6">
         <v>169</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D171" s="13" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>88</v>
+        <v>124</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>11</v>
@@ -5431,18 +5469,18 @@
       </c>
       <c r="I171" s="6"/>
     </row>
-    <row r="172" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="172" spans="2:9">
       <c r="B172" s="6">
         <v>170</v>
       </c>
       <c r="C172" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D172" s="13" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>88</v>
+        <v>124</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>11</v>
@@ -5456,18 +5494,18 @@
       </c>
       <c r="I172" s="6"/>
     </row>
-    <row r="173" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="173" spans="2:9">
       <c r="B173" s="6">
         <v>171</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D173" s="13" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>89</v>
+        <v>125</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>11</v>
@@ -5481,21 +5519,21 @@
       </c>
       <c r="I173" s="6"/>
     </row>
-    <row r="174" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:9">
       <c r="B174" s="6">
         <v>172</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D174" s="13" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>89</v>
+        <v>125</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G174" s="2">
         <v>95000</v>
@@ -5506,18 +5544,18 @@
       </c>
       <c r="I174" s="6"/>
     </row>
-    <row r="175" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="175" spans="2:9">
       <c r="B175" s="6">
         <v>173</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D175" s="13" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>90</v>
+        <v>126</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>11</v>
@@ -5531,21 +5569,21 @@
       </c>
       <c r="I175" s="6"/>
     </row>
-    <row r="176" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="176" spans="2:9">
       <c r="B176" s="6">
         <v>174</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D176" s="13" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>90</v>
+        <v>126</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G176" s="2">
         <v>100000</v>
@@ -5556,21 +5594,21 @@
       </c>
       <c r="I176" s="6"/>
     </row>
-    <row r="177" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="177" spans="2:9">
       <c r="B177" s="6">
         <v>175</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D177" s="13" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>90</v>
+        <v>126</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G177" s="2">
         <v>110000</v>
@@ -5581,134 +5619,324 @@
       </c>
       <c r="I177" s="6"/>
     </row>
-    <row r="178" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B178" s="6">
+    <row r="178" spans="2:9" s="19" customFormat="1">
+      <c r="B178" s="15">
         <v>176</v>
       </c>
-      <c r="C178" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D178" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="E178" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="F178" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G178" s="2">
+      <c r="C178" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D178" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="E178" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="F178" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G178" s="18">
         <v>100000</v>
       </c>
-      <c r="H178" s="2">
+      <c r="H178" s="18">
         <f t="shared" si="2"/>
         <v>145000</v>
       </c>
-      <c r="I178" s="6"/>
-    </row>
-    <row r="179" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B179" s="6"/>
-      <c r="C179" s="5"/>
-      <c r="D179" s="13"/>
-      <c r="E179" s="1"/>
-      <c r="F179" s="1"/>
-      <c r="G179" s="2"/>
-      <c r="H179" s="2"/>
+      <c r="I178" s="15"/>
+    </row>
+    <row r="179" spans="2:9">
+      <c r="B179" s="6">
+        <v>177</v>
+      </c>
+      <c r="C179" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="D179" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="E179" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F179" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G179" s="2">
+        <v>90000</v>
+      </c>
+      <c r="H179" s="2">
+        <f>G179+45000</f>
+        <v>135000</v>
+      </c>
       <c r="I179" s="6"/>
     </row>
-    <row r="180" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B180" s="6"/>
-      <c r="C180" s="5"/>
-      <c r="D180" s="13"/>
-      <c r="E180" s="1"/>
-      <c r="F180" s="1"/>
-      <c r="G180" s="2"/>
-      <c r="H180" s="2"/>
+    <row r="180" spans="2:9">
+      <c r="B180" s="6">
+        <v>178</v>
+      </c>
+      <c r="C180" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D180" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="E180" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="F180" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G180" s="2">
+        <v>85000</v>
+      </c>
+      <c r="H180" s="2">
+        <f>G180+45000</f>
+        <v>130000</v>
+      </c>
       <c r="I180" s="6"/>
     </row>
-    <row r="181" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B181" s="6"/>
-      <c r="C181" s="5"/>
-      <c r="D181" s="13"/>
-      <c r="E181" s="1"/>
-      <c r="F181" s="1"/>
-      <c r="G181" s="2"/>
-      <c r="H181" s="2"/>
+    <row r="181" spans="2:9" s="23" customFormat="1">
+      <c r="B181" s="6">
+        <v>179</v>
+      </c>
+      <c r="C181" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D181" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="E181" s="21" t="s">
+        <v>131</v>
+      </c>
+      <c r="F181" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="G181" s="22">
+        <v>80000</v>
+      </c>
+      <c r="H181" s="22">
+        <f t="shared" ref="H181:H192" si="3">G181+45000</f>
+        <v>125000</v>
+      </c>
       <c r="I181" s="6"/>
     </row>
-    <row r="182" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B182" s="6"/>
-      <c r="C182" s="5"/>
-      <c r="D182" s="13"/>
-      <c r="E182" s="1"/>
-      <c r="F182" s="1"/>
-      <c r="G182" s="2"/>
-      <c r="H182" s="2"/>
+    <row r="182" spans="2:9">
+      <c r="B182" s="6">
+        <v>180</v>
+      </c>
+      <c r="C182" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D182" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E182" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="F182" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G182" s="2">
+        <v>105000</v>
+      </c>
+      <c r="H182" s="2">
+        <f t="shared" si="3"/>
+        <v>150000</v>
+      </c>
       <c r="I182" s="6"/>
     </row>
-    <row r="183" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B183" s="6"/>
-      <c r="C183" s="5"/>
-      <c r="D183" s="13"/>
-      <c r="E183" s="1"/>
-      <c r="F183" s="1"/>
-      <c r="G183" s="2"/>
-      <c r="H183" s="2"/>
+    <row r="183" spans="2:9">
+      <c r="B183" s="6">
+        <v>181</v>
+      </c>
+      <c r="C183" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D183" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E183" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="F183" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G183" s="2">
+        <v>105000</v>
+      </c>
+      <c r="H183" s="2">
+        <f t="shared" si="3"/>
+        <v>150000</v>
+      </c>
       <c r="I183" s="6"/>
     </row>
-    <row r="184" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B184" s="6"/>
-      <c r="C184" s="5"/>
-      <c r="D184" s="13"/>
-      <c r="E184" s="1"/>
-      <c r="F184" s="1"/>
-      <c r="G184" s="2"/>
-      <c r="H184" s="2"/>
+    <row r="184" spans="2:9">
+      <c r="B184" s="6">
+        <v>182</v>
+      </c>
+      <c r="C184" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D184" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="E184" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F184" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G184" s="2">
+        <v>100000</v>
+      </c>
+      <c r="H184" s="2">
+        <f t="shared" si="3"/>
+        <v>145000</v>
+      </c>
       <c r="I184" s="6"/>
     </row>
-    <row r="185" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B185" s="6"/>
-      <c r="C185" s="5"/>
-      <c r="D185" s="13"/>
-      <c r="E185" s="1"/>
-      <c r="F185" s="1"/>
-      <c r="G185" s="2"/>
-      <c r="H185" s="2"/>
+    <row r="185" spans="2:9">
+      <c r="B185" s="6">
+        <v>183</v>
+      </c>
+      <c r="C185" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D185" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="E185" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="F185" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G185" s="2">
+        <v>100000</v>
+      </c>
+      <c r="H185" s="2">
+        <f t="shared" si="3"/>
+        <v>145000</v>
+      </c>
       <c r="I185" s="6"/>
     </row>
-    <row r="186" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B186" s="6"/>
-      <c r="C186" s="5"/>
-      <c r="D186" s="13"/>
-      <c r="E186" s="1"/>
-      <c r="F186" s="1"/>
-      <c r="G186" s="2"/>
-      <c r="H186" s="2"/>
+    <row r="186" spans="2:9">
+      <c r="B186" s="6">
+        <v>184</v>
+      </c>
+      <c r="C186" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D186" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="E186" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="F186" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G186" s="2">
+        <v>100000</v>
+      </c>
+      <c r="H186" s="2">
+        <f t="shared" si="3"/>
+        <v>145000</v>
+      </c>
       <c r="I186" s="6"/>
     </row>
-    <row r="187" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B187" s="6"/>
-      <c r="C187" s="5"/>
-      <c r="D187" s="13"/>
-      <c r="E187" s="1"/>
-      <c r="F187" s="1"/>
-      <c r="G187" s="2"/>
-      <c r="H187" s="2"/>
+    <row r="187" spans="2:9">
+      <c r="B187" s="6">
+        <v>185</v>
+      </c>
+      <c r="C187" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D187" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="E187" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F187" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G187" s="2">
+        <v>95000</v>
+      </c>
+      <c r="H187" s="2">
+        <f t="shared" si="3"/>
+        <v>140000</v>
+      </c>
       <c r="I187" s="6"/>
     </row>
-    <row r="188" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="188" spans="2:9">
       <c r="B188" s="6"/>
       <c r="C188" s="5"/>
       <c r="D188" s="13"/>
       <c r="E188" s="1"/>
       <c r="F188" s="1"/>
       <c r="G188" s="2"/>
-      <c r="H188" s="2"/>
+      <c r="H188" s="2">
+        <f t="shared" si="3"/>
+        <v>45000</v>
+      </c>
       <c r="I188" s="6"/>
     </row>
-    <row r="189" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="G189" s="3"/>
-      <c r="H189" s="3"/>
+    <row r="189" spans="2:9">
+      <c r="B189" s="6"/>
+      <c r="C189" s="5"/>
+      <c r="D189" s="13"/>
+      <c r="E189" s="1"/>
+      <c r="F189" s="1"/>
+      <c r="G189" s="2"/>
+      <c r="H189" s="2">
+        <f t="shared" si="3"/>
+        <v>45000</v>
+      </c>
+      <c r="I189" s="6"/>
+    </row>
+    <row r="190" spans="2:9">
+      <c r="B190" s="6"/>
+      <c r="C190" s="5"/>
+      <c r="D190" s="13"/>
+      <c r="E190" s="1"/>
+      <c r="F190" s="1"/>
+      <c r="G190" s="2"/>
+      <c r="H190" s="2">
+        <f t="shared" si="3"/>
+        <v>45000</v>
+      </c>
+      <c r="I190" s="6"/>
+    </row>
+    <row r="191" spans="2:9">
+      <c r="B191" s="6"/>
+      <c r="C191" s="5"/>
+      <c r="D191" s="13"/>
+      <c r="E191" s="1"/>
+      <c r="F191" s="1"/>
+      <c r="G191" s="2"/>
+      <c r="H191" s="2">
+        <f t="shared" si="3"/>
+        <v>45000</v>
+      </c>
+      <c r="I191" s="6"/>
+    </row>
+    <row r="192" spans="2:9">
+      <c r="B192" s="6"/>
+      <c r="C192" s="5"/>
+      <c r="D192" s="13"/>
+      <c r="E192" s="1"/>
+      <c r="F192" s="1"/>
+      <c r="G192" s="2"/>
+      <c r="H192" s="2">
+        <f t="shared" si="3"/>
+        <v>45000</v>
+      </c>
+      <c r="I192" s="6"/>
+    </row>
+    <row r="193" spans="7:8">
+      <c r="G193" s="3"/>
+      <c r="H193" s="3"/>
     </row>
   </sheetData>
   <autoFilter ref="B2:I180" xr:uid="{F75DB620-AF17-408B-81D4-431B9D551CF9}"/>

--- a/assets/LISTA ZAPATILLAS.xlsx
+++ b/assets/LISTA ZAPATILLAS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d8bfe2c87cad12b0/IA/MILENASHOES/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="79" documentId="13_ncr:1_{E0C42F5F-A3E4-4F22-AD40-E0497D996882}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BCA1ACB4-A517-45A0-B9B2-5B5BEBAE0C1E}"/>
+  <xr:revisionPtr revIDLastSave="82" documentId="13_ncr:1_{E0C42F5F-A3E4-4F22-AD40-E0497D996882}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20CDAEAB-ACCB-4C46-80BF-65540EB42DE1}"/>
   <bookViews>
     <workbookView xWindow="1545" yWindow="1125" windowWidth="15570" windowHeight="13710" xr2:uid="{B7A6A16F-7A19-4864-8939-1CF29A8D65F8}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="INVENTARIO" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">INVENTARIO!$B$2:$I$180</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">INVENTARIO!$B$2:$I$192</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -30,9 +30,10 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -447,7 +448,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -595,7 +596,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -892,7 +893,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F75DB620-AF17-408B-81D4-431B9D551CF9}">
   <dimension ref="B2:I193"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.42578125" customWidth="1"/>
     <col min="2" max="2" width="14.28515625" style="7" bestFit="1" customWidth="1"/>
@@ -904,7 +905,7 @@
     <col min="9" max="9" width="16" style="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9">
+    <row r="2" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B2" s="4" t="s">
         <v>0</v>
       </c>
@@ -930,7 +931,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="2:9">
+    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B3" s="5">
         <v>1</v>
       </c>
@@ -957,7 +958,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="2:9">
+    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B4" s="5">
         <v>2</v>
       </c>
@@ -984,7 +985,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="2:9">
+    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B5" s="5">
         <v>3</v>
       </c>
@@ -1011,7 +1012,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="2:9">
+    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B6" s="5">
         <v>4</v>
       </c>
@@ -1038,7 +1039,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="2:9">
+    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B7" s="5">
         <v>5</v>
       </c>
@@ -1065,7 +1066,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="2:9">
+    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B8" s="5">
         <v>6</v>
       </c>
@@ -1092,7 +1093,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="2:9">
+    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B9" s="5">
         <v>7</v>
       </c>
@@ -1119,7 +1120,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="2:9">
+    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B10" s="5">
         <v>8</v>
       </c>
@@ -1146,7 +1147,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="2:9">
+    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B11" s="5">
         <v>9</v>
       </c>
@@ -1173,7 +1174,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="2:9">
+    <row r="12" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B12" s="5">
         <v>10</v>
       </c>
@@ -1200,7 +1201,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="2:9">
+    <row r="13" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B13" s="5">
         <v>11</v>
       </c>
@@ -1227,7 +1228,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="2:9">
+    <row r="14" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B14" s="5">
         <v>12</v>
       </c>
@@ -1254,7 +1255,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="2:9">
+    <row r="15" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B15" s="5">
         <v>13</v>
       </c>
@@ -1281,7 +1282,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="2:9">
+    <row r="16" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B16" s="5">
         <v>14</v>
       </c>
@@ -1308,7 +1309,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="2:9">
+    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B17" s="5">
         <v>15</v>
       </c>
@@ -1335,7 +1336,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="2:9">
+    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B18" s="5">
         <v>16</v>
       </c>
@@ -1362,7 +1363,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="2:9">
+    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B19" s="5">
         <v>17</v>
       </c>
@@ -1389,7 +1390,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="2:9">
+    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B20" s="5">
         <v>18</v>
       </c>
@@ -1416,7 +1417,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="2:9">
+    <row r="21" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B21" s="5">
         <v>19</v>
       </c>
@@ -1443,7 +1444,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="2:9">
+    <row r="22" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B22" s="5">
         <v>20</v>
       </c>
@@ -1470,7 +1471,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="2:9">
+    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B23" s="5">
         <v>21</v>
       </c>
@@ -1497,7 +1498,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="2:9">
+    <row r="24" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B24" s="5">
         <v>22</v>
       </c>
@@ -1524,7 +1525,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="2:9">
+    <row r="25" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B25" s="5">
         <v>23</v>
       </c>
@@ -1551,7 +1552,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="2:9">
+    <row r="26" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B26" s="5">
         <v>24</v>
       </c>
@@ -1559,7 +1560,7 @@
         <v>13</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>37</v>
@@ -1578,7 +1579,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="2:9">
+    <row r="27" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B27" s="5">
         <v>25</v>
       </c>
@@ -1605,7 +1606,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="2:9">
+    <row r="28" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B28" s="5">
         <v>26</v>
       </c>
@@ -1632,7 +1633,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="29" spans="2:9">
+    <row r="29" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B29" s="5">
         <v>27</v>
       </c>
@@ -1659,7 +1660,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="30" spans="2:9">
+    <row r="30" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B30" s="5">
         <v>28</v>
       </c>
@@ -1686,7 +1687,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="31" spans="2:9">
+    <row r="31" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B31" s="5">
         <v>29</v>
       </c>
@@ -1713,7 +1714,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="32" spans="2:9">
+    <row r="32" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B32" s="5">
         <v>30</v>
       </c>
@@ -1740,7 +1741,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="33" spans="2:9">
+    <row r="33" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B33" s="5">
         <v>31</v>
       </c>
@@ -1767,7 +1768,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="34" spans="2:9">
+    <row r="34" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B34" s="5">
         <v>32</v>
       </c>
@@ -1794,7 +1795,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="35" spans="2:9">
+    <row r="35" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B35" s="5">
         <v>33</v>
       </c>
@@ -1821,7 +1822,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="36" spans="2:9">
+    <row r="36" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B36" s="5">
         <v>34</v>
       </c>
@@ -1848,7 +1849,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="37" spans="2:9">
+    <row r="37" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B37" s="5">
         <v>35</v>
       </c>
@@ -1875,7 +1876,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="38" spans="2:9">
+    <row r="38" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B38" s="5">
         <v>36</v>
       </c>
@@ -1902,7 +1903,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="2:9">
+    <row r="39" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B39" s="5">
         <v>37</v>
       </c>
@@ -1929,7 +1930,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="2:9">
+    <row r="40" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B40" s="5">
         <v>38</v>
       </c>
@@ -1956,7 +1957,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="41" spans="2:9">
+    <row r="41" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B41" s="5">
         <v>39</v>
       </c>
@@ -1983,7 +1984,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="42" spans="2:9">
+    <row r="42" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B42" s="5">
         <v>40</v>
       </c>
@@ -2010,7 +2011,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="43" spans="2:9">
+    <row r="43" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B43" s="5">
         <v>41</v>
       </c>
@@ -2037,7 +2038,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="44" spans="2:9">
+    <row r="44" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B44" s="5">
         <v>42</v>
       </c>
@@ -2064,7 +2065,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="45" spans="2:9">
+    <row r="45" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B45" s="5">
         <v>43</v>
       </c>
@@ -2091,7 +2092,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="46" spans="2:9">
+    <row r="46" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B46" s="5">
         <v>44</v>
       </c>
@@ -2118,7 +2119,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="47" spans="2:9">
+    <row r="47" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B47" s="5">
         <v>45</v>
       </c>
@@ -2145,7 +2146,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="48" spans="2:9">
+    <row r="48" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B48" s="5">
         <v>46</v>
       </c>
@@ -2172,7 +2173,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="49" spans="2:9">
+    <row r="49" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B49" s="5">
         <v>47</v>
       </c>
@@ -2199,7 +2200,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="50" spans="2:9">
+    <row r="50" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B50" s="5">
         <v>48</v>
       </c>
@@ -2226,7 +2227,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="51" spans="2:9">
+    <row r="51" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B51" s="5">
         <v>49</v>
       </c>
@@ -2253,7 +2254,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="52" spans="2:9">
+    <row r="52" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B52" s="5">
         <v>50</v>
       </c>
@@ -2280,7 +2281,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="53" spans="2:9">
+    <row r="53" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B53" s="5">
         <v>51</v>
       </c>
@@ -2307,7 +2308,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="54" spans="2:9">
+    <row r="54" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B54" s="5">
         <v>52</v>
       </c>
@@ -2334,7 +2335,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="55" spans="2:9">
+    <row r="55" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B55" s="5">
         <v>53</v>
       </c>
@@ -2361,7 +2362,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="56" spans="2:9">
+    <row r="56" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B56" s="5">
         <v>54</v>
       </c>
@@ -2388,7 +2389,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="57" spans="2:9">
+    <row r="57" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B57" s="5">
         <v>55</v>
       </c>
@@ -2415,7 +2416,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="58" spans="2:9">
+    <row r="58" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B58" s="5">
         <v>56</v>
       </c>
@@ -2442,7 +2443,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="59" spans="2:9">
+    <row r="59" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B59" s="5">
         <v>57</v>
       </c>
@@ -2469,7 +2470,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="60" spans="2:9">
+    <row r="60" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B60" s="5">
         <v>58</v>
       </c>
@@ -2496,7 +2497,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="61" spans="2:9">
+    <row r="61" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B61" s="5">
         <v>59</v>
       </c>
@@ -2523,7 +2524,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="62" spans="2:9">
+    <row r="62" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B62" s="5">
         <v>60</v>
       </c>
@@ -2550,7 +2551,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="63" spans="2:9">
+    <row r="63" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B63" s="5">
         <v>61</v>
       </c>
@@ -2577,7 +2578,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="64" spans="2:9">
+    <row r="64" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B64" s="5">
         <v>62</v>
       </c>
@@ -2604,7 +2605,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="65" spans="2:9">
+    <row r="65" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B65" s="5">
         <v>63</v>
       </c>
@@ -2631,7 +2632,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="66" spans="2:9">
+    <row r="66" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B66" s="5">
         <v>64</v>
       </c>
@@ -2658,7 +2659,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="67" spans="2:9">
+    <row r="67" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B67" s="5">
         <v>65</v>
       </c>
@@ -2685,7 +2686,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="68" spans="2:9">
+    <row r="68" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B68" s="5">
         <v>66</v>
       </c>
@@ -2712,7 +2713,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="69" spans="2:9">
+    <row r="69" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B69" s="5">
         <v>67</v>
       </c>
@@ -2739,7 +2740,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="70" spans="2:9">
+    <row r="70" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B70" s="5">
         <v>68</v>
       </c>
@@ -2766,7 +2767,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="71" spans="2:9">
+    <row r="71" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B71" s="5">
         <v>69</v>
       </c>
@@ -2793,7 +2794,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="72" spans="2:9">
+    <row r="72" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B72" s="5">
         <v>70</v>
       </c>
@@ -2820,7 +2821,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="73" spans="2:9">
+    <row r="73" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B73" s="5">
         <v>71</v>
       </c>
@@ -2847,7 +2848,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="74" spans="2:9">
+    <row r="74" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B74" s="5">
         <v>72</v>
       </c>
@@ -2874,7 +2875,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="75" spans="2:9">
+    <row r="75" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B75" s="5">
         <v>73</v>
       </c>
@@ -2901,7 +2902,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="76" spans="2:9">
+    <row r="76" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B76" s="5">
         <v>74</v>
       </c>
@@ -2928,7 +2929,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="77" spans="2:9">
+    <row r="77" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B77" s="5">
         <v>75</v>
       </c>
@@ -2955,7 +2956,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="78" spans="2:9">
+    <row r="78" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B78" s="5">
         <v>76</v>
       </c>
@@ -2982,7 +2983,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="79" spans="2:9">
+    <row r="79" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B79" s="5">
         <v>77</v>
       </c>
@@ -3009,7 +3010,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="80" spans="2:9">
+    <row r="80" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B80" s="5">
         <v>78</v>
       </c>
@@ -3036,7 +3037,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="81" spans="2:9">
+    <row r="81" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B81" s="5">
         <v>79</v>
       </c>
@@ -3063,7 +3064,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="82" spans="2:9">
+    <row r="82" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B82" s="5">
         <v>80</v>
       </c>
@@ -3090,7 +3091,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="83" spans="2:9">
+    <row r="83" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B83" s="5">
         <v>81</v>
       </c>
@@ -3117,7 +3118,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="84" spans="2:9">
+    <row r="84" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B84" s="5">
         <v>82</v>
       </c>
@@ -3144,7 +3145,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="85" spans="2:9">
+    <row r="85" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B85" s="5">
         <v>83</v>
       </c>
@@ -3171,7 +3172,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="86" spans="2:9">
+    <row r="86" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B86" s="5">
         <v>84</v>
       </c>
@@ -3198,7 +3199,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="87" spans="2:9">
+    <row r="87" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B87" s="5">
         <v>85</v>
       </c>
@@ -3225,7 +3226,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="88" spans="2:9">
+    <row r="88" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B88" s="5">
         <v>86</v>
       </c>
@@ -3252,7 +3253,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="89" spans="2:9">
+    <row r="89" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B89" s="5">
         <v>87</v>
       </c>
@@ -3279,7 +3280,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="90" spans="2:9">
+    <row r="90" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B90" s="5">
         <v>88</v>
       </c>
@@ -3306,7 +3307,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="91" spans="2:9">
+    <row r="91" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B91" s="5">
         <v>89</v>
       </c>
@@ -3333,7 +3334,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="92" spans="2:9">
+    <row r="92" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B92" s="5">
         <v>90</v>
       </c>
@@ -3360,7 +3361,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="93" spans="2:9">
+    <row r="93" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B93" s="5">
         <v>91</v>
       </c>
@@ -3387,7 +3388,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="94" spans="2:9">
+    <row r="94" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B94" s="5">
         <v>92</v>
       </c>
@@ -3414,7 +3415,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="95" spans="2:9">
+    <row r="95" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B95" s="5">
         <v>93</v>
       </c>
@@ -3441,7 +3442,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="96" spans="2:9">
+    <row r="96" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B96" s="5">
         <v>94</v>
       </c>
@@ -3468,7 +3469,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="97" spans="2:9">
+    <row r="97" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B97" s="5">
         <v>95</v>
       </c>
@@ -3495,7 +3496,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="98" spans="2:9">
+    <row r="98" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B98" s="5">
         <v>96</v>
       </c>
@@ -3522,7 +3523,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="99" spans="2:9">
+    <row r="99" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B99" s="5">
         <v>97</v>
       </c>
@@ -3549,7 +3550,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="100" spans="2:9">
+    <row r="100" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B100" s="5">
         <v>98</v>
       </c>
@@ -3576,7 +3577,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="101" spans="2:9">
+    <row r="101" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B101" s="5">
         <v>99</v>
       </c>
@@ -3603,7 +3604,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="102" spans="2:9">
+    <row r="102" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B102" s="5">
         <v>100</v>
       </c>
@@ -3630,7 +3631,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="103" spans="2:9">
+    <row r="103" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B103" s="5">
         <v>101</v>
       </c>
@@ -3657,7 +3658,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="104" spans="2:9">
+    <row r="104" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B104" s="5">
         <v>102</v>
       </c>
@@ -3684,7 +3685,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="105" spans="2:9">
+    <row r="105" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B105" s="5">
         <v>103</v>
       </c>
@@ -3711,7 +3712,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="106" spans="2:9">
+    <row r="106" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B106" s="5">
         <v>104</v>
       </c>
@@ -3738,7 +3739,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="107" spans="2:9">
+    <row r="107" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B107" s="5">
         <v>105</v>
       </c>
@@ -3765,7 +3766,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="108" spans="2:9">
+    <row r="108" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B108" s="5">
         <v>106</v>
       </c>
@@ -3792,7 +3793,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="109" spans="2:9">
+    <row r="109" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B109" s="5">
         <v>107</v>
       </c>
@@ -3819,7 +3820,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="110" spans="2:9">
+    <row r="110" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B110" s="5">
         <v>108</v>
       </c>
@@ -3846,7 +3847,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="111" spans="2:9">
+    <row r="111" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B111" s="5">
         <v>109</v>
       </c>
@@ -3873,7 +3874,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="112" spans="2:9">
+    <row r="112" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B112" s="5">
         <v>110</v>
       </c>
@@ -3900,7 +3901,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="113" spans="2:9">
+    <row r="113" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B113" s="5">
         <v>111</v>
       </c>
@@ -3927,7 +3928,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="114" spans="2:9">
+    <row r="114" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B114" s="5">
         <v>112</v>
       </c>
@@ -3954,7 +3955,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="115" spans="2:9">
+    <row r="115" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B115" s="5">
         <v>113</v>
       </c>
@@ -3981,7 +3982,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="116" spans="2:9">
+    <row r="116" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B116" s="5">
         <v>114</v>
       </c>
@@ -4008,7 +4009,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="117" spans="2:9">
+    <row r="117" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B117" s="5">
         <v>115</v>
       </c>
@@ -4035,7 +4036,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="118" spans="2:9">
+    <row r="118" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B118" s="5">
         <v>116</v>
       </c>
@@ -4062,7 +4063,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="119" spans="2:9">
+    <row r="119" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B119" s="5">
         <v>117</v>
       </c>
@@ -4089,7 +4090,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="120" spans="2:9">
+    <row r="120" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B120" s="5">
         <v>118</v>
       </c>
@@ -4116,7 +4117,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="121" spans="2:9">
+    <row r="121" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B121" s="5">
         <v>119</v>
       </c>
@@ -4143,7 +4144,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="122" spans="2:9">
+    <row r="122" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B122" s="5">
         <v>120</v>
       </c>
@@ -4170,7 +4171,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="123" spans="2:9">
+    <row r="123" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B123" s="5">
         <v>121</v>
       </c>
@@ -4197,7 +4198,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="124" spans="2:9">
+    <row r="124" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B124" s="5">
         <v>122</v>
       </c>
@@ -4224,7 +4225,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="125" spans="2:9">
+    <row r="125" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B125" s="5">
         <v>123</v>
       </c>
@@ -4251,7 +4252,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="126" spans="2:9">
+    <row r="126" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B126" s="5">
         <v>124</v>
       </c>
@@ -4278,7 +4279,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="127" spans="2:9">
+    <row r="127" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B127" s="5">
         <v>125</v>
       </c>
@@ -4305,7 +4306,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="128" spans="2:9">
+    <row r="128" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B128" s="6">
         <v>126</v>
       </c>
@@ -4332,7 +4333,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="129" spans="2:9">
+    <row r="129" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B129" s="6">
         <v>127</v>
       </c>
@@ -4359,7 +4360,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="130" spans="2:9">
+    <row r="130" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B130" s="6">
         <v>128</v>
       </c>
@@ -4386,7 +4387,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="131" spans="2:9">
+    <row r="131" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B131" s="6">
         <v>129</v>
       </c>
@@ -4413,7 +4414,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="132" spans="2:9">
+    <row r="132" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B132" s="6">
         <v>130</v>
       </c>
@@ -4440,7 +4441,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="133" spans="2:9">
+    <row r="133" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B133" s="6">
         <v>131</v>
       </c>
@@ -4467,7 +4468,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="134" spans="2:9">
+    <row r="134" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B134" s="6">
         <v>132</v>
       </c>
@@ -4494,7 +4495,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="135" spans="2:9">
+    <row r="135" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B135" s="6">
         <v>133</v>
       </c>
@@ -4521,7 +4522,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="136" spans="2:9">
+    <row r="136" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B136" s="6">
         <v>134</v>
       </c>
@@ -4548,7 +4549,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="137" spans="2:9">
+    <row r="137" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B137" s="6">
         <v>135</v>
       </c>
@@ -4575,7 +4576,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="138" spans="2:9">
+    <row r="138" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B138" s="6">
         <v>136</v>
       </c>
@@ -4602,7 +4603,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="139" spans="2:9">
+    <row r="139" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B139" s="6">
         <v>137</v>
       </c>
@@ -4629,7 +4630,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="140" spans="2:9">
+    <row r="140" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B140" s="6">
         <v>138</v>
       </c>
@@ -4656,7 +4657,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="141" spans="2:9">
+    <row r="141" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B141" s="6">
         <v>139</v>
       </c>
@@ -4683,7 +4684,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="142" spans="2:9">
+    <row r="142" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B142" s="6">
         <v>140</v>
       </c>
@@ -4710,7 +4711,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="143" spans="2:9">
+    <row r="143" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B143" s="6">
         <v>141</v>
       </c>
@@ -4737,7 +4738,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="144" spans="2:9">
+    <row r="144" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B144" s="6">
         <v>142</v>
       </c>
@@ -4764,7 +4765,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="145" spans="2:9">
+    <row r="145" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B145" s="6">
         <v>143</v>
       </c>
@@ -4791,7 +4792,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="146" spans="2:9">
+    <row r="146" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B146" s="6">
         <v>144</v>
       </c>
@@ -4818,7 +4819,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="147" spans="2:9">
+    <row r="147" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B147" s="6">
         <v>145</v>
       </c>
@@ -4845,7 +4846,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="148" spans="2:9">
+    <row r="148" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B148" s="6">
         <v>146</v>
       </c>
@@ -4872,7 +4873,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="149" spans="2:9">
+    <row r="149" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B149" s="6">
         <v>147</v>
       </c>
@@ -4899,7 +4900,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="150" spans="2:9">
+    <row r="150" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B150" s="6">
         <v>148</v>
       </c>
@@ -4926,7 +4927,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="151" spans="2:9">
+    <row r="151" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B151" s="6">
         <v>149</v>
       </c>
@@ -4953,7 +4954,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="152" spans="2:9">
+    <row r="152" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B152" s="6">
         <v>150</v>
       </c>
@@ -4980,7 +4981,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="153" spans="2:9">
+    <row r="153" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B153" s="6">
         <v>151</v>
       </c>
@@ -5007,7 +5008,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="154" spans="2:9">
+    <row r="154" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B154" s="6">
         <v>152</v>
       </c>
@@ -5034,7 +5035,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="155" spans="2:9">
+    <row r="155" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B155" s="6">
         <v>153</v>
       </c>
@@ -5061,7 +5062,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="156" spans="2:9">
+    <row r="156" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B156" s="6">
         <v>154</v>
       </c>
@@ -5088,7 +5089,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="157" spans="2:9">
+    <row r="157" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B157" s="6">
         <v>155</v>
       </c>
@@ -5115,7 +5116,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="158" spans="2:9">
+    <row r="158" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B158" s="6">
         <v>156</v>
       </c>
@@ -5142,7 +5143,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="159" spans="2:9">
+    <row r="159" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B159" s="8">
         <v>157</v>
       </c>
@@ -5169,7 +5170,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="160" spans="2:9">
+    <row r="160" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B160" s="6">
         <v>158</v>
       </c>
@@ -5194,7 +5195,7 @@
       </c>
       <c r="I160" s="6"/>
     </row>
-    <row r="161" spans="2:9">
+    <row r="161" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B161" s="6">
         <v>159</v>
       </c>
@@ -5219,7 +5220,7 @@
       </c>
       <c r="I161" s="6"/>
     </row>
-    <row r="162" spans="2:9">
+    <row r="162" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B162" s="6">
         <v>160</v>
       </c>
@@ -5244,7 +5245,7 @@
       </c>
       <c r="I162" s="6"/>
     </row>
-    <row r="163" spans="2:9">
+    <row r="163" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B163" s="6">
         <v>161</v>
       </c>
@@ -5269,7 +5270,7 @@
       </c>
       <c r="I163" s="6"/>
     </row>
-    <row r="164" spans="2:9">
+    <row r="164" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B164" s="6">
         <v>162</v>
       </c>
@@ -5294,7 +5295,7 @@
       </c>
       <c r="I164" s="6"/>
     </row>
-    <row r="165" spans="2:9">
+    <row r="165" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B165" s="6">
         <v>163</v>
       </c>
@@ -5319,7 +5320,7 @@
       </c>
       <c r="I165" s="6"/>
     </row>
-    <row r="166" spans="2:9">
+    <row r="166" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B166" s="6">
         <v>164</v>
       </c>
@@ -5344,7 +5345,7 @@
       </c>
       <c r="I166" s="6"/>
     </row>
-    <row r="167" spans="2:9">
+    <row r="167" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B167" s="6">
         <v>165</v>
       </c>
@@ -5369,7 +5370,7 @@
       </c>
       <c r="I167" s="6"/>
     </row>
-    <row r="168" spans="2:9">
+    <row r="168" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B168" s="6">
         <v>166</v>
       </c>
@@ -5394,7 +5395,7 @@
       </c>
       <c r="I168" s="6"/>
     </row>
-    <row r="169" spans="2:9">
+    <row r="169" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B169" s="6">
         <v>167</v>
       </c>
@@ -5419,7 +5420,7 @@
       </c>
       <c r="I169" s="6"/>
     </row>
-    <row r="170" spans="2:9">
+    <row r="170" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B170" s="6">
         <v>168</v>
       </c>
@@ -5444,7 +5445,7 @@
       </c>
       <c r="I170" s="6"/>
     </row>
-    <row r="171" spans="2:9">
+    <row r="171" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B171" s="6">
         <v>169</v>
       </c>
@@ -5469,7 +5470,7 @@
       </c>
       <c r="I171" s="6"/>
     </row>
-    <row r="172" spans="2:9">
+    <row r="172" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B172" s="6">
         <v>170</v>
       </c>
@@ -5494,7 +5495,7 @@
       </c>
       <c r="I172" s="6"/>
     </row>
-    <row r="173" spans="2:9">
+    <row r="173" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B173" s="6">
         <v>171</v>
       </c>
@@ -5519,7 +5520,7 @@
       </c>
       <c r="I173" s="6"/>
     </row>
-    <row r="174" spans="2:9">
+    <row r="174" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B174" s="6">
         <v>172</v>
       </c>
@@ -5544,7 +5545,7 @@
       </c>
       <c r="I174" s="6"/>
     </row>
-    <row r="175" spans="2:9">
+    <row r="175" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B175" s="6">
         <v>173</v>
       </c>
@@ -5569,7 +5570,7 @@
       </c>
       <c r="I175" s="6"/>
     </row>
-    <row r="176" spans="2:9">
+    <row r="176" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B176" s="6">
         <v>174</v>
       </c>
@@ -5594,7 +5595,7 @@
       </c>
       <c r="I176" s="6"/>
     </row>
-    <row r="177" spans="2:9">
+    <row r="177" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B177" s="6">
         <v>175</v>
       </c>
@@ -5619,7 +5620,7 @@
       </c>
       <c r="I177" s="6"/>
     </row>
-    <row r="178" spans="2:9" s="19" customFormat="1">
+    <row r="178" spans="2:9" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B178" s="15">
         <v>176</v>
       </c>
@@ -5644,7 +5645,7 @@
       </c>
       <c r="I178" s="15"/>
     </row>
-    <row r="179" spans="2:9">
+    <row r="179" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B179" s="6">
         <v>177</v>
       </c>
@@ -5669,7 +5670,7 @@
       </c>
       <c r="I179" s="6"/>
     </row>
-    <row r="180" spans="2:9">
+    <row r="180" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B180" s="6">
         <v>178</v>
       </c>
@@ -5694,7 +5695,7 @@
       </c>
       <c r="I180" s="6"/>
     </row>
-    <row r="181" spans="2:9" s="23" customFormat="1">
+    <row r="181" spans="2:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B181" s="6">
         <v>179</v>
       </c>
@@ -5719,7 +5720,7 @@
       </c>
       <c r="I181" s="6"/>
     </row>
-    <row r="182" spans="2:9">
+    <row r="182" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B182" s="6">
         <v>180</v>
       </c>
@@ -5744,7 +5745,7 @@
       </c>
       <c r="I182" s="6"/>
     </row>
-    <row r="183" spans="2:9">
+    <row r="183" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B183" s="6">
         <v>181</v>
       </c>
@@ -5769,7 +5770,7 @@
       </c>
       <c r="I183" s="6"/>
     </row>
-    <row r="184" spans="2:9">
+    <row r="184" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B184" s="6">
         <v>182</v>
       </c>
@@ -5794,7 +5795,7 @@
       </c>
       <c r="I184" s="6"/>
     </row>
-    <row r="185" spans="2:9">
+    <row r="185" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B185" s="6">
         <v>183</v>
       </c>
@@ -5819,7 +5820,7 @@
       </c>
       <c r="I185" s="6"/>
     </row>
-    <row r="186" spans="2:9">
+    <row r="186" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B186" s="6">
         <v>184</v>
       </c>
@@ -5844,7 +5845,7 @@
       </c>
       <c r="I186" s="6"/>
     </row>
-    <row r="187" spans="2:9">
+    <row r="187" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B187" s="6">
         <v>185</v>
       </c>
@@ -5869,7 +5870,7 @@
       </c>
       <c r="I187" s="6"/>
     </row>
-    <row r="188" spans="2:9">
+    <row r="188" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B188" s="6"/>
       <c r="C188" s="5"/>
       <c r="D188" s="13"/>
@@ -5882,7 +5883,7 @@
       </c>
       <c r="I188" s="6"/>
     </row>
-    <row r="189" spans="2:9">
+    <row r="189" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B189" s="6"/>
       <c r="C189" s="5"/>
       <c r="D189" s="13"/>
@@ -5895,7 +5896,7 @@
       </c>
       <c r="I189" s="6"/>
     </row>
-    <row r="190" spans="2:9">
+    <row r="190" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B190" s="6"/>
       <c r="C190" s="5"/>
       <c r="D190" s="13"/>
@@ -5908,7 +5909,7 @@
       </c>
       <c r="I190" s="6"/>
     </row>
-    <row r="191" spans="2:9">
+    <row r="191" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B191" s="6"/>
       <c r="C191" s="5"/>
       <c r="D191" s="13"/>
@@ -5921,7 +5922,7 @@
       </c>
       <c r="I191" s="6"/>
     </row>
-    <row r="192" spans="2:9">
+    <row r="192" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B192" s="6"/>
       <c r="C192" s="5"/>
       <c r="D192" s="13"/>
@@ -5934,12 +5935,12 @@
       </c>
       <c r="I192" s="6"/>
     </row>
-    <row r="193" spans="7:8">
+    <row r="193" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G193" s="3"/>
       <c r="H193" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="B2:I180" xr:uid="{F75DB620-AF17-408B-81D4-431B9D551CF9}"/>
+  <autoFilter ref="B2:I192" xr:uid="{F75DB620-AF17-408B-81D4-431B9D551CF9}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/assets/LISTA ZAPATILLAS.xlsx
+++ b/assets/LISTA ZAPATILLAS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manuel\Desktop\MILENASHOES\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4434F384-E11A-4F4F-A508-CB7C2FBCCA13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D218201-E70E-43EF-9572-FA07924B256B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8205" yWindow="1935" windowWidth="15495" windowHeight="11295" xr2:uid="{B7A6A16F-7A19-4864-8939-1CF29A8D65F8}"/>
   </bookViews>
